--- a/tdot-lcca/verification/new_project_CKV/CKV_Runway17-35_LCCA_run.xlsx
+++ b/tdot-lcca/verification/new_project_CKV/CKV_Runway17-35_LCCA_run.xlsx
@@ -28,7 +28,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'General Information'!$A$1:$J$48</definedName>
-    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$U$78</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$U$112</definedName>
     <definedName function="false" hidden="false" name="Airport_Name" vbProcedure="false">'General Information'!$D$9</definedName>
     <definedName function="false" hidden="false" name="Pay_Items" vbProcedure="false">Pay_Items!$C$3:$D$59</definedName>
     <definedName function="false" hidden="false" name="Pay_Item_List" vbProcedure="false">Pay_Items!$B$2:$C$4</definedName>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="935">
   <si>
     <t xml:space="preserve">  Grey cells are yours: C4 to C7 project data (filled from General Information), F4 and F5 closure days, C13 to C22 pay items and E13 to E22 quantities. Everything else calculates.</t>
   </si>
@@ -2201,7 +2201,67 @@
     <t xml:space="preserve">Calendar year</t>
   </si>
   <si>
+    <t xml:space="preserve">PAVEMENT SECTION (inches): mainline, then the reading if the quantities also cover the shoulder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subbase (P-154)</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to read: 1 shows where each alternative's cost sits; 2 whether the lowest-cost alternative holds at other discount rates (FAA now uses the OMB A-94 real rate, about 2%; 7% was the rule before 2022); 3 and 4 when the money is spent and when the higher first cost is paid back; 5 how often and how long the runway closes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregate base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asphalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAVEMENT SECTION  (read back from the quantities already entered; nothing here changes a cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asphalt unit weight, pcf:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only asphalt needs an assumption: 145 pcf reproduces the Murfreesboro section to the hundredth of an inch. Volume items convert directly, and concrete carries its thickness in the pay-item name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoulder reading (blank unless shoulder area is entered)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface course (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregate base (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subbase (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated subgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total section (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavation (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavation check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section from the quantities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness is not an input. Volume items give inches = 36 x C.Y. / mainline S.Y.; asphalt gives inches = 2,666.67 x tons / (pcf x mainline S.Y.); items measured by area carry no implied thickness. The last column is the section as the quantities describe it: paste it into the alternative description so the two can never disagree. The read-back divides by the mainline area only, so the excavation check is what catches a quantity that also covers the shoulder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charts 6 and 7 stack the layers as they sit in the ground, surface on top. Chart 7 stays empty unless a shoulder area is entered on General Information, and then shows the same quantities spread over mainline plus shoulder, which is the lower bound on each thickness.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference sheet: nothing here feeds the calculation.</t>
@@ -2859,7 +2919,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0"/>
@@ -2875,10 +2935,11 @@
     <numFmt numFmtId="176" formatCode="0.00%"/>
     <numFmt numFmtId="177" formatCode="0.00\%"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
-    <numFmt numFmtId="179" formatCode="\$#,##0,,\M"/>
-    <numFmt numFmtId="180" formatCode="#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="0.00"/>
+    <numFmt numFmtId="180" formatCode="\$#,##0,,\M"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3113,6 +3174,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -3489,7 +3557,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4050,6 +4118,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="179" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4066,11 +4146,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4151,13 +4231,13 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF186A3B"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF7F6000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF8B8B8B"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF8EA9DB"/>
@@ -4167,27 +4247,27 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFF39C7A"/>
       <rgbColor rgb="FF0563C1"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFC6CBD0"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FFDAE3F3"/>
-      <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FFC00000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF8B8B8B"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFA5A5A5"/>
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FFEAF2FB"/>
       <rgbColor rgb="FFDCDCDC"/>
       <rgbColor rgb="FF8FAADC"/>
-      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FFC8A96E"/>
       <rgbColor rgb="FFB8B6AE"/>
       <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF6DA7EC"/>
-      <rgbColor rgb="FFA5A5A5"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FFDCCBA0"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FFEB6834"/>
       <rgbColor rgb="FF646464"/>
@@ -4195,11 +4275,11 @@
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF1D2733"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF4A4A4A"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF1F4E9C"/>
-      <rgbColor rgb="FF1D2733"/>
+      <rgbColor rgb="FF3A3A3A"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -4764,11 +4844,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="100"/>
-        <c:axId val="28914137"/>
-        <c:axId val="5331312"/>
+        <c:axId val="52519032"/>
+        <c:axId val="21492574"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28914137"/>
+        <c:axId val="52519032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4800,7 +4880,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5331312"/>
+        <c:crossAx val="21492574"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4808,7 +4888,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5331312"/>
+        <c:axId val="21492574"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4850,7 +4930,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28914137"/>
+        <c:crossAx val="52519032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5988,11 +6068,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="86678828"/>
-        <c:axId val="53152981"/>
+        <c:axId val="25577386"/>
+        <c:axId val="86770330"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="86678828"/>
+        <c:axId val="25577386"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6024,7 +6104,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53152981"/>
+        <c:crossAx val="86770330"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6032,7 +6112,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53152981"/>
+        <c:axId val="86770330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6064,7 +6144,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86678828"/>
+        <c:crossAx val="25577386"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7179,11 +7259,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="34255744"/>
-        <c:axId val="22246610"/>
+        <c:axId val="5253529"/>
+        <c:axId val="88710124"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34255744"/>
+        <c:axId val="5253529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7215,7 +7295,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22246610"/>
+        <c:crossAx val="88710124"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7223,7 +7303,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22246610"/>
+        <c:axId val="88710124"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7255,7 +7335,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34255744"/>
+        <c:crossAx val="5253529"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7319,6 +7399,1160 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>6. Pavement section, mainline (inches, surface on top)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Subbase (P-154)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="dccba0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="dccba0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$75:$AA$75</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$76:$AA$76</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.0000599997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.0000599997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aggregate base</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c8a96e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="c8a96e"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$75:$AA$75</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$77:$AA$77</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.99991000045</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.99991000045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W78</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Asphalt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3a3a3a"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="3a3a3a"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$75:$AA$75</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$78:$AA$78</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>9.10340287264081</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W79</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concrete</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c6cbd0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="c6cbd0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$75:$AA$75</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$79:$AA$79</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:overlap val="100"/>
+        <c:axId val="50680498"/>
+        <c:axId val="44033443"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50680498"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6480">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="44033443"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="44033443"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>inches</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="6480">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50680498"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>7. Pavement section with the shoulder (empty unless a shoulder area is entered)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W83</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Subbase (P-154)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="dccba0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="dccba0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$82:$AA$82</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$83:$AA$83</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W84</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aggregate base</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c8a96e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="c8a96e"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$82:$AA$82</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$84:$AA$84</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W85</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Asphalt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3a3a3a"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="3a3a3a"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$82:$AA$82</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$85:$AA$85</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!W86</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Concrete</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c6cbd0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="c6cbd0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$X$82:$AA$82</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alternative 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alternative 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alt 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Alt 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$X$86:$AA$86</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:overlap val="100"/>
+        <c:axId val="68635605"/>
+        <c:axId val="35114819"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="68635605"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6480">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35114819"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="35114819"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>inches</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="6480">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="68635605"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
               <a:defRPr b="0" lang="en-US" sz="1400" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
@@ -7866,11 +9100,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="100"/>
-        <c:axId val="11985630"/>
-        <c:axId val="4239796"/>
+        <c:axId val="13237561"/>
+        <c:axId val="36645242"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11985630"/>
+        <c:axId val="13237561"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7902,7 +9136,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4239796"/>
+        <c:crossAx val="36645242"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7910,7 +9144,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4239796"/>
+        <c:axId val="36645242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7952,7 +9186,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11985630"/>
+        <c:crossAx val="13237561"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8006,7 +9240,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -8565,11 +9799,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="100"/>
-        <c:axId val="21530761"/>
-        <c:axId val="69666740"/>
+        <c:axId val="30683793"/>
+        <c:axId val="76597931"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21530761"/>
+        <c:axId val="30683793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8601,7 +9835,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69666740"/>
+        <c:crossAx val="76597931"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8609,7 +9843,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69666740"/>
+        <c:axId val="76597931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8651,7 +9885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21530761"/>
+        <c:crossAx val="30683793"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9264,11 +10498,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="100"/>
-        <c:axId val="14659367"/>
-        <c:axId val="50422676"/>
+        <c:axId val="77604443"/>
+        <c:axId val="25242653"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14659367"/>
+        <c:axId val="77604443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9300,7 +10534,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50422676"/>
+        <c:crossAx val="25242653"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9308,7 +10542,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50422676"/>
+        <c:axId val="25242653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9350,7 +10584,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14659367"/>
+        <c:crossAx val="77604443"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9707,11 +10941,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="95093842"/>
-        <c:axId val="28963080"/>
+        <c:axId val="67131451"/>
+        <c:axId val="87837349"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95093842"/>
+        <c:axId val="67131451"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9743,7 +10977,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28963080"/>
+        <c:crossAx val="87837349"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9751,7 +10985,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28963080"/>
+        <c:axId val="87837349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9793,7 +11027,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95093842"/>
+        <c:crossAx val="67131451"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10150,11 +11384,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="5914296"/>
-        <c:axId val="74784722"/>
+        <c:axId val="31925918"/>
+        <c:axId val="20007432"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5914296"/>
+        <c:axId val="31925918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10186,7 +11420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74784722"/>
+        <c:crossAx val="20007432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10194,7 +11428,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74784722"/>
+        <c:axId val="20007432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10236,7 +11470,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5914296"/>
+        <c:crossAx val="31925918"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10593,11 +11827,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="35630473"/>
-        <c:axId val="76427462"/>
+        <c:axId val="26684446"/>
+        <c:axId val="89388454"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35630473"/>
+        <c:axId val="26684446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10629,7 +11863,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76427462"/>
+        <c:crossAx val="89388454"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10637,7 +11871,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76427462"/>
+        <c:axId val="89388454"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10679,7 +11913,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35630473"/>
+        <c:crossAx val="26684446"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10956,11 +12190,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="9769942"/>
-        <c:axId val="34941621"/>
+        <c:axId val="29971399"/>
+        <c:axId val="31056745"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9769942"/>
+        <c:axId val="29971399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10992,7 +12226,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34941621"/>
+        <c:crossAx val="31056745"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11000,7 +12234,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34941621"/>
+        <c:axId val="31056745"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11042,7 +12276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9769942"/>
+        <c:crossAx val="29971399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11603,11 +12837,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="32094489"/>
-        <c:axId val="10498334"/>
+        <c:axId val="62384185"/>
+        <c:axId val="1183258"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32094489"/>
+        <c:axId val="62384185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11639,7 +12873,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10498334"/>
+        <c:crossAx val="1183258"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11647,7 +12881,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10498334"/>
+        <c:axId val="1183258"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11679,7 +12913,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32094489"/>
+        <c:crossAx val="62384185"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12671,11 +13905,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="329251"/>
-        <c:axId val="66202510"/>
+        <c:axId val="42909600"/>
+        <c:axId val="63825810"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="329251"/>
+        <c:axId val="42909600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12707,7 +13941,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66202510"/>
+        <c:crossAx val="63825810"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12715,7 +13949,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66202510"/>
+        <c:axId val="63825810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12747,7 +13981,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="329251"/>
+        <c:crossAx val="42909600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13862,11 +15096,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="11246272"/>
-        <c:axId val="50097528"/>
+        <c:axId val="44136842"/>
+        <c:axId val="1234502"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11246272"/>
+        <c:axId val="44136842"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13898,7 +15132,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50097528"/>
+        <c:crossAx val="1234502"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13906,7 +15140,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50097528"/>
+        <c:axId val="1234502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13938,7 +15172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11246272"/>
+        <c:crossAx val="44136842"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16094,6 +17328,66 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>156240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>423360</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>178560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="Summary Chart 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11112480" y="17345160"/>
+        <a:ext cx="5579640" cy="2879640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>156240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>601200</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>178560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="Summary Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="21247200" y="17345160"/>
+        <a:ext cx="5579640" cy="2879640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -16114,7 +17408,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="17" name="Chart 1"/>
+        <xdr:cNvPr id="19" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -16589,7 +17883,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="18" name="Chart 1"/>
+        <xdr:cNvPr id="20" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -28404,7 +29698,7 @@
     <tabColor rgb="FF2A78D6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AJ77"/>
+  <dimension ref="A1:AJ108"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -31445,9 +32739,423 @@
         <v>0</v>
       </c>
     </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W74" s="127" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W75" s="128" t="s">
+        <v>698</v>
+      </c>
+      <c r="X75" s="128" t="str">
+        <f aca="false">X$4</f>
+        <v>Alternative 1</v>
+      </c>
+      <c r="Y75" s="128" t="str">
+        <f aca="false">Y$4</f>
+        <v>Alternative 2</v>
+      </c>
+      <c r="Z75" s="128" t="str">
+        <f aca="false">Z$4</f>
+        <v>Alt 3</v>
+      </c>
+      <c r="AA75" s="128" t="str">
+        <f aca="false">AA$4</f>
+        <v>Alt 4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W76" s="133" t="s">
+        <v>699</v>
+      </c>
+      <c r="X76" s="140" t="n">
+        <f aca="false">IF($G$4="",0,IFERROR(J83,0))</f>
+        <v>8.0000599997</v>
+      </c>
+      <c r="Y76" s="140" t="n">
+        <f aca="false">IF($G$5="",0,IFERROR(J84,0))</f>
+        <v>8.0000599997</v>
+      </c>
+      <c r="Z76" s="140" t="n">
+        <f aca="false">IF($G$6="",0,IFERROR(J85,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AA76" s="140" t="n">
+        <f aca="false">IF($G$7="",0,IFERROR(J86,0))</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G77" s="59" t="s">
-        <v>697</v>
+        <v>700</v>
+      </c>
+      <c r="W77" s="133" t="s">
+        <v>701</v>
+      </c>
+      <c r="X77" s="140" t="n">
+        <f aca="false">IF($G$4="",0,IFERROR(I83,0))</f>
+        <v>5.99991000045</v>
+      </c>
+      <c r="Y77" s="140" t="n">
+        <f aca="false">IF($G$5="",0,IFERROR(I84,0))</f>
+        <v>5.99991000045</v>
+      </c>
+      <c r="Z77" s="140" t="n">
+        <f aca="false">IF($G$6="",0,IFERROR(I85,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AA77" s="140" t="n">
+        <f aca="false">IF($G$7="",0,IFERROR(I86,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W78" s="133" t="s">
+        <v>702</v>
+      </c>
+      <c r="X78" s="140" t="n">
+        <f aca="true">IF($G$4="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"TON")&gt;0,H83,0),0))</f>
+        <v>9.10340287264081</v>
+      </c>
+      <c r="Y78" s="140" t="n">
+        <f aca="true">IF($G$5="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"TON")&gt;0,H84,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="140" t="n">
+        <f aca="true">IF($G$6="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"TON")&gt;0,H85,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="AA78" s="140" t="n">
+        <f aca="true">IF($G$7="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"TON")&gt;0,H86,0),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W79" s="133" t="s">
+        <v>703</v>
+      </c>
+      <c r="X79" s="140" t="n">
+        <f aca="true">IF($G$4="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"TON")&gt;0,0,H83),0))</f>
+        <v>0</v>
+      </c>
+      <c r="Y79" s="140" t="n">
+        <f aca="true">IF($G$5="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"TON")&gt;0,0,H84),0))</f>
+        <v>9</v>
+      </c>
+      <c r="Z79" s="140" t="n">
+        <f aca="true">IF($G$6="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"TON")&gt;0,0,H85),0))</f>
+        <v>0</v>
+      </c>
+      <c r="AA79" s="140" t="n">
+        <f aca="true">IF($G$7="",0,IFERROR(IF(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"TON")&gt;0,0,H86),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G80" s="126" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G81" s="127" t="s">
+        <v>705</v>
+      </c>
+      <c r="J81" s="141" t="n">
+        <v>145</v>
+      </c>
+      <c r="K81" s="59" t="s">
+        <v>706</v>
+      </c>
+      <c r="W81" s="127" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G82" s="128" t="s">
+        <v>661</v>
+      </c>
+      <c r="H82" s="128" t="s">
+        <v>708</v>
+      </c>
+      <c r="I82" s="128" t="s">
+        <v>709</v>
+      </c>
+      <c r="J82" s="128" t="s">
+        <v>710</v>
+      </c>
+      <c r="K82" s="128" t="s">
+        <v>711</v>
+      </c>
+      <c r="L82" s="128" t="s">
+        <v>712</v>
+      </c>
+      <c r="M82" s="128" t="s">
+        <v>713</v>
+      </c>
+      <c r="N82" s="128" t="s">
+        <v>714</v>
+      </c>
+      <c r="O82" s="128"/>
+      <c r="P82" s="128" t="s">
+        <v>715</v>
+      </c>
+      <c r="W82" s="128" t="s">
+        <v>698</v>
+      </c>
+      <c r="X82" s="128" t="str">
+        <f aca="false">X$4</f>
+        <v>Alternative 1</v>
+      </c>
+      <c r="Y82" s="128" t="str">
+        <f aca="false">Y$4</f>
+        <v>Alternative 2</v>
+      </c>
+      <c r="Z82" s="128" t="str">
+        <f aca="false">Z$4</f>
+        <v>Alt 3</v>
+      </c>
+      <c r="AA82" s="128" t="str">
+        <f aca="false">AA$4</f>
+        <v>Alt 4</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G83" s="129" t="str">
+        <f aca="false">IF($G$4="","",$H$4)</f>
+        <v>Alternative 1</v>
+      </c>
+      <c r="H83" s="142" t="n">
+        <f aca="true">IF($G$4="","",IF(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"TON")&gt;0,SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"TON")*2666.6667/($J$81*'General Information'!$D$26),IFERROR(VALUE(TRIM(SUBSTITUTE(MID(IFERROR(INDEX(INDIRECT("'"&amp;$G$4&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$4&amp;"'!$C$13:$C$22"),0)),""),FIND(",",IFERROR(INDEX(INDIRECT("'"&amp;$G$4&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$4&amp;"'!$C$13:$C$22"),0)),""))+1,99),"-inch",""))),0)))</f>
+        <v>9.10340287264081</v>
+      </c>
+      <c r="I83" s="142" t="n">
+        <f aca="true">IF($G$4="","",36*(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-2*")+SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-3*"))/'General Information'!$D$26)</f>
+        <v>5.99991000045</v>
+      </c>
+      <c r="J83" s="142" t="n">
+        <f aca="true">IF($G$4="","",36*SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-154*")/'General Information'!$D$26)</f>
+        <v>8.0000599997</v>
+      </c>
+      <c r="K83" s="142" t="str">
+        <f aca="true">IF($G$4="","",IF(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-155*")+SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-156*")+SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-157*")+SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-158*")&gt;0,"yes","-"))</f>
+        <v>yes</v>
+      </c>
+      <c r="L83" s="142" t="n">
+        <f aca="false">IF($G$4="","",H83+I83+J83)</f>
+        <v>23.1033728727908</v>
+      </c>
+      <c r="M83" s="142" t="n">
+        <f aca="true">IF($G$4="","",36*SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),"P-152*")/'General Information'!$D$26)</f>
+        <v>0</v>
+      </c>
+      <c r="N83" s="129" t="str">
+        <f aca="false">IF($G$4="","",IF(M83=0,"no excavation item",IF(ABS(M83-L83)&lt;=0.5,"agrees","differs by "&amp;TEXT(M83-L83,"0.0")&amp;" in")))</f>
+        <v>no excavation item</v>
+      </c>
+      <c r="P83" s="129" t="str">
+        <f aca="true">IF($G$4="","",TEXT(H83,"0")&amp;""" "&amp;IF(SUMIFS(INDIRECT("'"&amp;$G$4&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$4&amp;"'!$D$13:$D$22"),"TON")&gt;0,IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),MATCH("P-4*",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),MATCH("P-501*",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),0)),5),"-",""),""))&amp;IF(I83&gt;0," on "&amp;TEXT(I83,"0")&amp;""" "&amp;IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),MATCH("P-2*",INDIRECT("'"&amp;$G$4&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),"")&amp;IF(J83&gt;0," on "&amp;TEXT(J83,"0")&amp;""" P154",""))</f>
+        <v>9" P401 on 6" P209 on 8" P154</v>
+      </c>
+      <c r="W83" s="133" t="s">
+        <v>699</v>
+      </c>
+      <c r="X83" s="140" t="n">
+        <f aca="false">IFERROR(X76*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y83" s="140" t="n">
+        <f aca="false">IFERROR(Y76*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="140" t="n">
+        <f aca="false">IFERROR(Z76*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA83" s="140" t="n">
+        <f aca="false">IFERROR(AA76*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G84" s="129" t="str">
+        <f aca="false">IF($G$5="","",$H$5)</f>
+        <v>Alternative 2</v>
+      </c>
+      <c r="H84" s="142" t="n">
+        <f aca="true">IF($G$5="","",IF(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"TON")&gt;0,SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"TON")*2666.6667/($J$81*'General Information'!$D$26),IFERROR(VALUE(TRIM(SUBSTITUTE(MID(IFERROR(INDEX(INDIRECT("'"&amp;$G$5&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$5&amp;"'!$C$13:$C$22"),0)),""),FIND(",",IFERROR(INDEX(INDIRECT("'"&amp;$G$5&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$5&amp;"'!$C$13:$C$22"),0)),""))+1,99),"-inch",""))),0)))</f>
+        <v>9</v>
+      </c>
+      <c r="I84" s="142" t="n">
+        <f aca="true">IF($G$5="","",36*(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-2*")+SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-3*"))/'General Information'!$D$26)</f>
+        <v>5.99991000045</v>
+      </c>
+      <c r="J84" s="142" t="n">
+        <f aca="true">IF($G$5="","",36*SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-154*")/'General Information'!$D$26)</f>
+        <v>8.0000599997</v>
+      </c>
+      <c r="K84" s="142" t="str">
+        <f aca="true">IF($G$5="","",IF(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-155*")+SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-156*")+SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-157*")+SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-158*")&gt;0,"yes","-"))</f>
+        <v>yes</v>
+      </c>
+      <c r="L84" s="142" t="n">
+        <f aca="false">IF($G$5="","",H84+I84+J84)</f>
+        <v>22.99997000015</v>
+      </c>
+      <c r="M84" s="142" t="n">
+        <f aca="true">IF($G$5="","",36*SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),"P-152*")/'General Information'!$D$26)</f>
+        <v>0</v>
+      </c>
+      <c r="N84" s="129" t="str">
+        <f aca="false">IF($G$5="","",IF(M84=0,"no excavation item",IF(ABS(M84-L84)&lt;=0.5,"agrees","differs by "&amp;TEXT(M84-L84,"0.0")&amp;" in")))</f>
+        <v>no excavation item</v>
+      </c>
+      <c r="P84" s="129" t="str">
+        <f aca="true">IF($G$5="","",TEXT(H84,"0")&amp;""" "&amp;IF(SUMIFS(INDIRECT("'"&amp;$G$5&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$5&amp;"'!$D$13:$D$22"),"TON")&gt;0,IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),MATCH("P-4*",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),MATCH("P-501*",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),0)),5),"-",""),""))&amp;IF(I84&gt;0," on "&amp;TEXT(I84,"0")&amp;""" "&amp;IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),MATCH("P-2*",INDIRECT("'"&amp;$G$5&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),"")&amp;IF(J84&gt;0," on "&amp;TEXT(J84,"0")&amp;""" P154",""))</f>
+        <v>9" P501 on 6" P209 on 8" P154</v>
+      </c>
+      <c r="W84" s="133" t="s">
+        <v>701</v>
+      </c>
+      <c r="X84" s="140" t="n">
+        <f aca="false">IFERROR(X77*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="140" t="n">
+        <f aca="false">IFERROR(Y77*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z84" s="140" t="n">
+        <f aca="false">IFERROR(Z77*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA84" s="140" t="n">
+        <f aca="false">IFERROR(AA77*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G85" s="129" t="str">
+        <f aca="false">IF($G$6="","",$H$6)</f>
+        <v/>
+      </c>
+      <c r="H85" s="142" t="str">
+        <f aca="true">IF($G$6="","",IF(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"TON")&gt;0,SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"TON")*2666.6667/($J$81*'General Information'!$D$26),IFERROR(VALUE(TRIM(SUBSTITUTE(MID(IFERROR(INDEX(INDIRECT("'"&amp;$G$6&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$6&amp;"'!$C$13:$C$22"),0)),""),FIND(",",IFERROR(INDEX(INDIRECT("'"&amp;$G$6&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$6&amp;"'!$C$13:$C$22"),0)),""))+1,99),"-inch",""))),0)))</f>
+        <v/>
+      </c>
+      <c r="I85" s="142" t="str">
+        <f aca="true">IF($G$6="","",36*(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-2*")+SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-3*"))/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="J85" s="142" t="str">
+        <f aca="true">IF($G$6="","",36*SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-154*")/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="K85" s="142" t="str">
+        <f aca="true">IF($G$6="","",IF(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-155*")+SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-156*")+SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-157*")+SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-158*")&gt;0,"yes","-"))</f>
+        <v/>
+      </c>
+      <c r="L85" s="142" t="str">
+        <f aca="false">IF($G$6="","",H85+I85+J85)</f>
+        <v/>
+      </c>
+      <c r="M85" s="142" t="str">
+        <f aca="true">IF($G$6="","",36*SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),"P-152*")/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="N85" s="129" t="str">
+        <f aca="false">IF($G$6="","",IF(M85=0,"no excavation item",IF(ABS(M85-L85)&lt;=0.5,"agrees","differs by "&amp;TEXT(M85-L85,"0.0")&amp;" in")))</f>
+        <v/>
+      </c>
+      <c r="P85" s="129" t="str">
+        <f aca="true">IF($G$6="","",TEXT(H85,"0")&amp;""" "&amp;IF(SUMIFS(INDIRECT("'"&amp;$G$6&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$6&amp;"'!$D$13:$D$22"),"TON")&gt;0,IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),MATCH("P-4*",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),MATCH("P-501*",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),0)),5),"-",""),""))&amp;IF(I85&gt;0," on "&amp;TEXT(I85,"0")&amp;""" "&amp;IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),MATCH("P-2*",INDIRECT("'"&amp;$G$6&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),"")&amp;IF(J85&gt;0," on "&amp;TEXT(J85,"0")&amp;""" P154",""))</f>
+        <v/>
+      </c>
+      <c r="W85" s="133" t="s">
+        <v>702</v>
+      </c>
+      <c r="X85" s="140" t="n">
+        <f aca="false">IFERROR(X78*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="140" t="n">
+        <f aca="false">IFERROR(Y78*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z85" s="140" t="n">
+        <f aca="false">IFERROR(Z78*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="140" t="n">
+        <f aca="false">IFERROR(AA78*IF('General Information'!$D$27&gt;0,'General Information'!$D$26/('General Information'!$D$26+'General Information'!$D$27),0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G86" s="129" t="str">
+        <f aca="false">IF($G$7="","",$H$7)</f>
+        <v/>
+      </c>
+      <c r="H86" s="142" t="str">
+        <f aca="true">IF($G$7="","",IF(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"TON")&gt;0,SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"TON")*2666.6667/($J$81*'General Information'!$D$26),IFERROR(VALUE(TRIM(SUBSTITUTE(MID(IFERROR(INDEX(INDIRECT("'"&amp;$G$7&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$7&amp;"'!$C$13:$C$22"),0)),""),FIND(",",IFERROR(INDEX(INDIRECT("'"&amp;$G$7&amp;"'!$C$13:$C$22"),MATCH("Concrete Pavement*",INDIRECT("'"&amp;$G$7&amp;"'!$C$13:$C$22"),0)),""))+1,99),"-inch",""))),0)))</f>
+        <v/>
+      </c>
+      <c r="I86" s="142" t="str">
+        <f aca="true">IF($G$7="","",36*(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-2*")+SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-3*"))/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="J86" s="142" t="str">
+        <f aca="true">IF($G$7="","",36*SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-154*")/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="K86" s="142" t="str">
+        <f aca="true">IF($G$7="","",IF(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-155*")+SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-156*")+SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-157*")+SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"S.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-158*")&gt;0,"yes","-"))</f>
+        <v/>
+      </c>
+      <c r="L86" s="142" t="str">
+        <f aca="false">IF($G$7="","",H86+I86+J86)</f>
+        <v/>
+      </c>
+      <c r="M86" s="142" t="str">
+        <f aca="true">IF($G$7="","",36*SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"C.Y.",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),"P-152*")/'General Information'!$D$26)</f>
+        <v/>
+      </c>
+      <c r="N86" s="129" t="str">
+        <f aca="false">IF($G$7="","",IF(M86=0,"no excavation item",IF(ABS(M86-L86)&lt;=0.5,"agrees","differs by "&amp;TEXT(M86-L86,"0.0")&amp;" in")))</f>
+        <v/>
+      </c>
+      <c r="P86" s="129" t="str">
+        <f aca="true">IF($G$7="","",TEXT(H86,"0")&amp;""" "&amp;IF(SUMIFS(INDIRECT("'"&amp;$G$7&amp;"'!$E$13:$E$22"),INDIRECT("'"&amp;$G$7&amp;"'!$D$13:$D$22"),"TON")&gt;0,IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),MATCH("P-4*",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),MATCH("P-501*",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),0)),5),"-",""),""))&amp;IF(I86&gt;0," on "&amp;TEXT(I86,"0")&amp;""" "&amp;IFERROR(SUBSTITUTE(LEFT(INDEX(INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),MATCH("P-2*",INDIRECT("'"&amp;$G$7&amp;"'!$B$13:$B$22"),0)),5),"-",""),""),"")&amp;IF(J86&gt;0," on "&amp;TEXT(J86,"0")&amp;""" P154",""))</f>
+        <v/>
+      </c>
+      <c r="W86" s="133" t="s">
+        <v>703</v>
+      </c>
+      <c r="X86" s="140" t="n">
+        <f aca="false">IFERROR(X79*IF('General Information'!$D$27&gt;0,1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y86" s="140" t="n">
+        <f aca="false">IFERROR(Y79*IF('General Information'!$D$27&gt;0,1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z86" s="140" t="n">
+        <f aca="false">IFERROR(Z79*IF('General Information'!$D$27&gt;0,1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA86" s="140" t="n">
+        <f aca="false">IFERROR(AA79*IF('General Information'!$D$27&gt;0,1,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G87" s="59" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G108" s="59" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -31502,28 +33210,28 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="59" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="126" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="140" t="s">
-        <v>700</v>
-      </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
+      <c r="A4" s="143" t="s">
+        <v>720</v>
+      </c>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="135" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="B6" s="136"/>
       <c r="C6" s="136"/>
@@ -31537,7 +33245,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="128" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="C7" s="128" t="s">
         <v>20</v>
@@ -31548,235 +33256,235 @@
       <c r="E7" s="128"/>
       <c r="F7" s="128"/>
       <c r="G7" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="141" t="s">
-        <v>704</v>
-      </c>
-      <c r="B8" s="142" t="n">
+      <c r="A8" s="144" t="s">
+        <v>724</v>
+      </c>
+      <c r="B8" s="145" t="n">
         <v>78</v>
       </c>
-      <c r="C8" s="141" t="s">
-        <v>705</v>
-      </c>
-      <c r="D8" s="143" t="n">
+      <c r="C8" s="144" t="s">
+        <v>725</v>
+      </c>
+      <c r="D8" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="144" t="str">
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inventory-Existing-System-Conditions-March-2021-v3.pdf","https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inven")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inven</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="141" t="s">
-        <v>706</v>
-      </c>
-      <c r="B9" s="141" t="s">
-        <v>707</v>
-      </c>
-      <c r="C9" s="141" t="s">
-        <v>705</v>
-      </c>
-      <c r="D9" s="143" t="n">
+      <c r="A9" s="144" t="s">
+        <v>726</v>
+      </c>
+      <c r="B9" s="144" t="s">
+        <v>727</v>
+      </c>
+      <c r="C9" s="144" t="s">
+        <v>725</v>
+      </c>
+      <c r="D9" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E9" s="141"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="144" t="str">
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inventory-Existing-System-Conditions-March-2021-v3.pdf","https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inven")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2021/03/Updated-TASP-Inven</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="141" t="s">
-        <v>708</v>
-      </c>
-      <c r="B10" s="142" t="n">
+      <c r="A10" s="144" t="s">
+        <v>728</v>
+      </c>
+      <c r="B10" s="145" t="n">
         <v>69</v>
       </c>
-      <c r="C10" s="141" t="s">
-        <v>705</v>
-      </c>
-      <c r="D10" s="143" t="n">
+      <c r="C10" s="144" t="s">
+        <v>725</v>
+      </c>
+      <c r="D10" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="144" t="str">
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-Classifications-and-NPIAS-Evaluation.pdf","https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="141" t="s">
-        <v>709</v>
-      </c>
-      <c r="B11" s="141" t="s">
-        <v>710</v>
-      </c>
-      <c r="C11" s="141" t="s">
-        <v>705</v>
-      </c>
-      <c r="D11" s="143" t="n">
+      <c r="A11" s="144" t="s">
+        <v>729</v>
+      </c>
+      <c r="B11" s="144" t="s">
+        <v>730</v>
+      </c>
+      <c r="C11" s="144" t="s">
+        <v>725</v>
+      </c>
+      <c r="D11" s="146" t="n">
         <v>2022</v>
       </c>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="144" t="str">
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.appliedpavement.com/tennessee-apms","https://www.appliedpavement.com/tennessee-apms")</f>
         <v>https://www.appliedpavement.com/tennessee-apms</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="141" t="s">
-        <v>711</v>
-      </c>
-      <c r="B12" s="141" t="s">
-        <v>712</v>
-      </c>
-      <c r="C12" s="141" t="s">
-        <v>713</v>
-      </c>
-      <c r="D12" s="143" t="n">
+      <c r="A12" s="144" t="s">
+        <v>731</v>
+      </c>
+      <c r="B12" s="144" t="s">
+        <v>732</v>
+      </c>
+      <c r="C12" s="144" t="s">
+        <v>733</v>
+      </c>
+      <c r="D12" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="144" t="str">
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tn.gov/content/dam/tn/tdot/aeronautics/TN%20Airport%20Management%20Guide%20FINAL.pdf","https://www.tn.gov/content/dam/tn/tdot/aeronautics/TN%20Airport%20Mana")</f>
         <v>https://www.tn.gov/content/dam/tn/tdot/aeronautics/TN%20Airport%20Mana</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="141" t="s">
-        <v>714</v>
-      </c>
-      <c r="B13" s="142" t="n">
+      <c r="A13" s="144" t="s">
+        <v>734</v>
+      </c>
+      <c r="B13" s="145" t="n">
         <v>70865874</v>
       </c>
-      <c r="C13" s="141" t="s">
-        <v>715</v>
-      </c>
-      <c r="D13" s="143" t="n">
+      <c r="C13" s="144" t="s">
+        <v>735</v>
+      </c>
+      <c r="D13" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="144" t="str">
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate-Chapter.pdf","https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="141" t="s">
-        <v>716</v>
-      </c>
-      <c r="B14" s="142" t="n">
+      <c r="A14" s="144" t="s">
+        <v>736</v>
+      </c>
+      <c r="B14" s="145" t="n">
         <v>173117648</v>
       </c>
-      <c r="C14" s="141" t="s">
-        <v>715</v>
-      </c>
-      <c r="D14" s="143" t="n">
+      <c r="C14" s="144" t="s">
+        <v>735</v>
+      </c>
+      <c r="D14" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="144" t="str">
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate-Chapter.pdf","https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2021/09/TASP-Cost-Estimate</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="141" t="s">
-        <v>717</v>
-      </c>
-      <c r="B15" s="141" t="s">
-        <v>718</v>
-      </c>
-      <c r="C15" s="141"/>
-      <c r="D15" s="143" t="n">
+      <c r="A15" s="144" t="s">
+        <v>737</v>
+      </c>
+      <c r="B15" s="144" t="s">
+        <v>738</v>
+      </c>
+      <c r="C15" s="144"/>
+      <c r="D15" s="146" t="n">
         <v>2023</v>
       </c>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="144" t="str">
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tn.gov/content/dam/tn/tdot/documents/170-02.pdf","https://www.tn.gov/content/dam/tn/tdot/documents/170-02.pdf")</f>
         <v>https://www.tn.gov/content/dam/tn/tdot/documents/170-02.pdf</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="141" t="s">
-        <v>719</v>
-      </c>
-      <c r="B16" s="141" t="s">
-        <v>720</v>
-      </c>
-      <c r="C16" s="141"/>
-      <c r="D16" s="143" t="n">
+      <c r="A16" s="144" t="s">
+        <v>739</v>
+      </c>
+      <c r="B16" s="144" t="s">
+        <v>740</v>
+      </c>
+      <c r="C16" s="144"/>
+      <c r="D16" s="146" t="n">
         <v>2024</v>
       </c>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="144" t="str">
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tn.gov/tdot/aeronautics/apmm-contract.html","https://www.tn.gov/tdot/aeronautics/apmm-contract.html")</f>
         <v>https://www.tn.gov/tdot/aeronautics/apmm-contract.html</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="141" t="s">
-        <v>721</v>
-      </c>
-      <c r="B17" s="141" t="s">
-        <v>722</v>
-      </c>
-      <c r="C17" s="141"/>
-      <c r="D17" s="143" t="n">
+      <c r="A17" s="144" t="s">
+        <v>741</v>
+      </c>
+      <c r="B17" s="144" t="s">
+        <v>742</v>
+      </c>
+      <c r="C17" s="144"/>
+      <c r="D17" s="146" t="n">
         <v>2022</v>
       </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="144" t="str">
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="147" t="str">
         <f aca="false">HYPERLINK("https://idea.appliedpavement.com/hosting/tennessee/statewide-summary/inventory-area/area-by-airport-table.html","https://idea.appliedpavement.com/hosting/tennessee/statewide-summary/i")</f>
         <v>https://idea.appliedpavement.com/hosting/tennessee/statewide-summary/i</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="141" t="s">
-        <v>723</v>
-      </c>
-      <c r="B18" s="141" t="s">
-        <v>724</v>
-      </c>
-      <c r="C18" s="141"/>
-      <c r="D18" s="143" t="n">
+      <c r="A18" s="144" t="s">
+        <v>743</v>
+      </c>
+      <c r="B18" s="144" t="s">
+        <v>744</v>
+      </c>
+      <c r="C18" s="144"/>
+      <c r="D18" s="146" t="n">
         <v>2024</v>
       </c>
-      <c r="E18" s="141"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="144" t="str">
+      <c r="E18" s="144"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/sites/faa.gov/files/airports/planning_capacity/npias/current/ARP-NPIAS-2025-2029-Appendix-A.pdf","https://www.faa.gov/sites/faa.gov/files/airports/planning_capacity/npi")</f>
         <v>https://www.faa.gov/sites/faa.gov/files/airports/planning_capacity/npi</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="140" t="s">
-        <v>725</v>
-      </c>
-      <c r="B19" s="140"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="140"/>
+      <c r="A19" s="143" t="s">
+        <v>745</v>
+      </c>
+      <c r="B19" s="143"/>
+      <c r="C19" s="143"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="143"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="135" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="B21" s="136"/>
       <c r="C21" s="136"/>
@@ -31787,242 +33495,242 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="128" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="B22" s="128" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="128" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="D22" s="128" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="E22" s="128" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="F22" s="128" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="G22" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="141" t="s">
-        <v>732</v>
-      </c>
-      <c r="B23" s="141" t="s">
-        <v>733</v>
-      </c>
-      <c r="C23" s="141" t="s">
-        <v>734</v>
-      </c>
-      <c r="D23" s="142" t="n">
+      <c r="A23" s="144" t="s">
+        <v>752</v>
+      </c>
+      <c r="B23" s="144" t="s">
+        <v>753</v>
+      </c>
+      <c r="C23" s="144" t="s">
+        <v>754</v>
+      </c>
+      <c r="D23" s="145" t="n">
         <v>52811</v>
       </c>
-      <c r="E23" s="141" t="s">
-        <v>735</v>
-      </c>
-      <c r="F23" s="141" t="s">
-        <v>736</v>
-      </c>
-      <c r="G23" s="144" t="str">
+      <c r="E23" s="144" t="s">
+        <v>755</v>
+      </c>
+      <c r="F23" s="144" t="s">
+        <v>756</v>
+      </c>
+      <c r="G23" s="147" t="str">
         <f aca="false">HYPERLINK("https://en.wikipedia.org/wiki/Murfreesboro_Municipal_Airport","https://en.wikipedia.org/wiki/Murfreesboro_Municipal_Airport")</f>
         <v>https://en.wikipedia.org/wiki/Murfreesboro_Municipal_Airport</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="141" t="s">
-        <v>737</v>
-      </c>
-      <c r="B24" s="141" t="s">
-        <v>733</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>738</v>
-      </c>
-      <c r="D24" s="142" t="n">
+      <c r="A24" s="144" t="s">
+        <v>757</v>
+      </c>
+      <c r="B24" s="144" t="s">
+        <v>753</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>758</v>
+      </c>
+      <c r="D24" s="145" t="n">
         <v>61144</v>
       </c>
-      <c r="E24" s="141" t="s">
-        <v>735</v>
-      </c>
-      <c r="F24" s="141"/>
-      <c r="G24" s="144" t="str">
+      <c r="E24" s="144" t="s">
+        <v>755</v>
+      </c>
+      <c r="F24" s="144"/>
+      <c r="G24" s="147" t="str">
         <f aca="false">HYPERLINK("https://en.wikipedia.org/wiki/Shelbyville_Municipal_Airport_(Tennessee)","https://en.wikipedia.org/wiki/Shelbyville_Municipal_Airport_(Tennessee")</f>
         <v>https://en.wikipedia.org/wiki/Shelbyville_Municipal_Airport_(Tennessee</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="141" t="s">
-        <v>739</v>
-      </c>
-      <c r="B25" s="141" t="s">
-        <v>740</v>
-      </c>
-      <c r="C25" s="141" t="s">
-        <v>741</v>
-      </c>
-      <c r="D25" s="142" t="n">
+      <c r="A25" s="144" t="s">
+        <v>759</v>
+      </c>
+      <c r="B25" s="144" t="s">
+        <v>760</v>
+      </c>
+      <c r="C25" s="144" t="s">
+        <v>761</v>
+      </c>
+      <c r="D25" s="145" t="n">
         <v>45883</v>
       </c>
-      <c r="E25" s="141" t="s">
-        <v>742</v>
-      </c>
-      <c r="F25" s="141" t="s">
-        <v>743</v>
-      </c>
-      <c r="G25" s="144" t="str">
+      <c r="E25" s="144" t="s">
+        <v>762</v>
+      </c>
+      <c r="F25" s="144" t="s">
+        <v>763</v>
+      </c>
+      <c r="G25" s="147" t="str">
         <f aca="false">HYPERLINK("https://en.wikipedia.org/wiki/Gatlinburg%E2%80%93Pigeon_Forge_Airport","https://en.wikipedia.org/wiki/Gatlinburg%E2%80%93Pigeon_Forge_Airport")</f>
         <v>https://en.wikipedia.org/wiki/Gatlinburg%E2%80%93Pigeon_Forge_Airport</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="141" t="s">
-        <v>744</v>
-      </c>
-      <c r="B26" s="141" t="s">
-        <v>745</v>
-      </c>
-      <c r="C26" s="141" t="s">
-        <v>746</v>
-      </c>
-      <c r="D26" s="142" t="n">
+      <c r="A26" s="144" t="s">
+        <v>764</v>
+      </c>
+      <c r="B26" s="144" t="s">
+        <v>765</v>
+      </c>
+      <c r="C26" s="144" t="s">
+        <v>766</v>
+      </c>
+      <c r="D26" s="145" t="n">
         <v>66656</v>
       </c>
-      <c r="E26" s="141" t="s">
-        <v>735</v>
-      </c>
-      <c r="F26" s="141" t="s">
-        <v>747</v>
-      </c>
-      <c r="G26" s="144" t="str">
+      <c r="E26" s="144" t="s">
+        <v>755</v>
+      </c>
+      <c r="F26" s="144" t="s">
+        <v>767</v>
+      </c>
+      <c r="G26" s="147" t="str">
         <f aca="false">HYPERLINK("https://en.wikipedia.org/wiki/Clarksville%E2%80%93Montgomery_County_Regional_Airport","https://en.wikipedia.org/wiki/Clarksville%E2%80%93Montgomery_County_Re")</f>
         <v>https://en.wikipedia.org/wiki/Clarksville%E2%80%93Montgomery_County_Re</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="141" t="s">
-        <v>748</v>
-      </c>
-      <c r="B27" s="141" t="s">
-        <v>749</v>
-      </c>
-      <c r="C27" s="141" t="s">
-        <v>750</v>
-      </c>
-      <c r="D27" s="142" t="n">
+      <c r="A27" s="144" t="s">
+        <v>768</v>
+      </c>
+      <c r="B27" s="144" t="s">
+        <v>769</v>
+      </c>
+      <c r="C27" s="144" t="s">
+        <v>770</v>
+      </c>
+      <c r="D27" s="145" t="n">
         <v>100083</v>
       </c>
-      <c r="E27" s="141" t="s">
-        <v>751</v>
-      </c>
-      <c r="F27" s="141" t="s">
-        <v>752</v>
-      </c>
-      <c r="G27" s="144" t="str">
+      <c r="E27" s="144" t="s">
+        <v>771</v>
+      </c>
+      <c r="F27" s="144" t="s">
+        <v>772</v>
+      </c>
+      <c r="G27" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.wbbjtv.com/2024/08/28/mckellar-sipes-regional-airport-set-to-complete-runway-2-20-paving-preparing-for-new-jet-service/","https://www.wbbjtv.com/2024/08/28/mckellar-sipes-regional-airport-set-")</f>
         <v>https://www.wbbjtv.com/2024/08/28/mckellar-sipes-regional-airport-set-</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="141" t="s">
-        <v>753</v>
-      </c>
-      <c r="B28" s="141" t="s">
-        <v>754</v>
-      </c>
-      <c r="C28" s="141" t="s">
+      <c r="A28" s="144" t="s">
+        <v>773</v>
+      </c>
+      <c r="B28" s="144" t="s">
+        <v>774</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>775</v>
+      </c>
+      <c r="D28" s="145" t="n">
+        <v>61622</v>
+      </c>
+      <c r="E28" s="144" t="s">
         <v>755</v>
       </c>
-      <c r="D28" s="142" t="n">
-        <v>61622</v>
-      </c>
-      <c r="E28" s="141" t="s">
-        <v>735</v>
-      </c>
-      <c r="F28" s="141" t="s">
-        <v>756</v>
-      </c>
-      <c r="G28" s="144" t="str">
+      <c r="F28" s="144" t="s">
+        <v>776</v>
+      </c>
+      <c r="G28" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-grand-opening","https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-gr")</f>
         <v>https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-gr</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="141" t="s">
-        <v>753</v>
-      </c>
-      <c r="B29" s="141" t="s">
-        <v>757</v>
-      </c>
-      <c r="C29" s="141" t="s">
-        <v>758</v>
-      </c>
-      <c r="D29" s="142" t="n">
+      <c r="A29" s="144" t="s">
+        <v>773</v>
+      </c>
+      <c r="B29" s="144" t="s">
+        <v>777</v>
+      </c>
+      <c r="C29" s="144" t="s">
+        <v>778</v>
+      </c>
+      <c r="D29" s="145" t="n">
         <v>133967</v>
       </c>
-      <c r="E29" s="141" t="s">
-        <v>735</v>
-      </c>
-      <c r="F29" s="141" t="s">
-        <v>759</v>
-      </c>
-      <c r="G29" s="144" t="str">
+      <c r="E29" s="144" t="s">
+        <v>755</v>
+      </c>
+      <c r="F29" s="144" t="s">
+        <v>779</v>
+      </c>
+      <c r="G29" s="147" t="str">
         <f aca="false">HYPERLINK("https://en.wikipedia.org/wiki/Smyrna_Airport_(Tennessee)","https://en.wikipedia.org/wiki/Smyrna_Airport_(Tennessee)")</f>
         <v>https://en.wikipedia.org/wiki/Smyrna_Airport_(Tennessee)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="141" t="s">
-        <v>760</v>
-      </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="141" t="s">
-        <v>761</v>
-      </c>
-      <c r="D30" s="141" t="s">
-        <v>762</v>
-      </c>
-      <c r="E30" s="141"/>
-      <c r="F30" s="141" t="s">
-        <v>763</v>
-      </c>
-      <c r="G30" s="144" t="str">
+      <c r="A30" s="144" t="s">
+        <v>780</v>
+      </c>
+      <c r="B30" s="144"/>
+      <c r="C30" s="144" t="s">
+        <v>781</v>
+      </c>
+      <c r="D30" s="144" t="s">
+        <v>782</v>
+      </c>
+      <c r="E30" s="144"/>
+      <c r="F30" s="144" t="s">
+        <v>783</v>
+      </c>
+      <c r="G30" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-Classifications-and-NPIAS-Evaluation.pdf","https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-")</f>
         <v>https://www.tasp2040.com/wp-content/uploads/2020/12/Chapter-7-Airport-</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="141" t="s">
-        <v>764</v>
-      </c>
-      <c r="B31" s="141"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141" t="s">
-        <v>765</v>
-      </c>
-      <c r="G31" s="141" t="s">
-        <v>766</v>
+      <c r="A31" s="144" t="s">
+        <v>784</v>
+      </c>
+      <c r="B31" s="144"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144" t="s">
+        <v>785</v>
+      </c>
+      <c r="G31" s="144" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="140" t="s">
-        <v>767</v>
-      </c>
-      <c r="B32" s="140"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="140"/>
+      <c r="A32" s="143" t="s">
+        <v>787</v>
+      </c>
+      <c r="B32" s="143"/>
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="143"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="135" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="B34" s="136"/>
       <c r="C34" s="136"/>
@@ -32033,269 +33741,269 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="128" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="B35" s="128" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="C35" s="128" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="128" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="E35" s="128" t="s">
         <v>35</v>
       </c>
       <c r="F35" s="128" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="G35" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="141" t="s">
-        <v>773</v>
-      </c>
-      <c r="B36" s="145" t="n">
+      <c r="A36" s="144" t="s">
+        <v>793</v>
+      </c>
+      <c r="B36" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Asphalt Surface Course",Pay_Items!$D:$F,3,0),"")</f>
         <v>130</v>
       </c>
-      <c r="C36" s="141" t="s">
-        <v>774</v>
-      </c>
-      <c r="D36" s="141" t="s">
-        <v>775</v>
-      </c>
-      <c r="E36" s="142" t="n">
+      <c r="C36" s="144" t="s">
+        <v>794</v>
+      </c>
+      <c r="D36" s="144" t="s">
+        <v>795</v>
+      </c>
+      <c r="E36" s="145" t="n">
         <v>2025</v>
       </c>
-      <c r="F36" s="141" t="s">
-        <v>776</v>
-      </c>
-      <c r="G36" s="144" t="str">
+      <c r="F36" s="144" t="s">
+        <v>796</v>
+      </c>
+      <c r="G36" s="147" t="str">
         <f aca="false">HYPERLINK("https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Rehab_Twy_A.pdf","https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Reha")</f>
         <v>https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Reha</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="141" t="s">
-        <v>777</v>
-      </c>
-      <c r="B37" s="145" t="n">
+      <c r="A37" s="144" t="s">
+        <v>797</v>
+      </c>
+      <c r="B37" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Asphalt Base Course",Pay_Items!$D:$F,3,0),"")</f>
         <v>120</v>
       </c>
-      <c r="C37" s="141" t="s">
-        <v>774</v>
-      </c>
-      <c r="D37" s="141" t="s">
-        <v>778</v>
-      </c>
-      <c r="E37" s="141"/>
-      <c r="F37" s="141"/>
-      <c r="G37" s="144" t="str">
+      <c r="C37" s="144" t="s">
+        <v>794</v>
+      </c>
+      <c r="D37" s="144" t="s">
+        <v>798</v>
+      </c>
+      <c r="E37" s="144"/>
+      <c r="F37" s="144"/>
+      <c r="G37" s="147" t="str">
         <f aca="false">HYPERLINK("https://aeronautics.sc.gov/airport-development/sc-airport-capital-project-bid-tabulations","https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj")</f>
         <v>https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="141" t="s">
-        <v>779</v>
-      </c>
-      <c r="B38" s="145" t="n">
+      <c r="A38" s="144" t="s">
+        <v>799</v>
+      </c>
+      <c r="B38" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Concrete Pavement, 9-inch",Pay_Items!$D:$F,3,0),"")</f>
         <v>85</v>
       </c>
-      <c r="C38" s="141" t="s">
-        <v>780</v>
-      </c>
-      <c r="D38" s="141" t="s">
-        <v>781</v>
-      </c>
-      <c r="E38" s="142" t="n">
+      <c r="C38" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="D38" s="144" t="s">
+        <v>801</v>
+      </c>
+      <c r="E38" s="145" t="n">
         <v>2023</v>
       </c>
-      <c r="F38" s="141" t="s">
-        <v>782</v>
-      </c>
-      <c r="G38" s="144" t="str">
+      <c r="F38" s="144" t="s">
+        <v>802</v>
+      </c>
+      <c r="G38" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.dot.state.mn.us/aero/planning/documents/sasp/saspappendixf.pdf","https://www.dot.state.mn.us/aero/planning/documents/sasp/saspappendixf")</f>
         <v>https://www.dot.state.mn.us/aero/planning/documents/sasp/saspappendixf</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="141" t="s">
-        <v>783</v>
-      </c>
-      <c r="B39" s="145" t="n">
+      <c r="A39" s="144" t="s">
+        <v>803</v>
+      </c>
+      <c r="B39" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Crushed Aggregate Base Course",Pay_Items!$D:$F,3,0),"")</f>
         <v>65</v>
       </c>
-      <c r="C39" s="141" t="s">
-        <v>784</v>
-      </c>
-      <c r="D39" s="141" t="s">
-        <v>785</v>
-      </c>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-      <c r="G39" s="144" t="str">
+      <c r="C39" s="144" t="s">
+        <v>804</v>
+      </c>
+      <c r="D39" s="144" t="s">
+        <v>805</v>
+      </c>
+      <c r="E39" s="144"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="147" t="str">
         <f aca="false">HYPERLINK("https://aeronautics.sc.gov/airport-development/sc-airport-capital-project-bid-tabulations","https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj")</f>
         <v>https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="141" t="s">
-        <v>786</v>
-      </c>
-      <c r="B40" s="145" t="n">
+      <c r="A40" s="144" t="s">
+        <v>806</v>
+      </c>
+      <c r="B40" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Subbase Course",Pay_Items!$D:$F,3,0),"")</f>
         <v>55</v>
       </c>
-      <c r="C40" s="141" t="s">
-        <v>784</v>
-      </c>
-      <c r="D40" s="141" t="s">
-        <v>785</v>
-      </c>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="144" t="str">
+      <c r="C40" s="144" t="s">
+        <v>804</v>
+      </c>
+      <c r="D40" s="144" t="s">
+        <v>805</v>
+      </c>
+      <c r="E40" s="144"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="147" t="str">
         <f aca="false">HYPERLINK("https://aeronautics.sc.gov/airport-development/sc-airport-capital-project-bid-tabulations","https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj")</f>
         <v>https://aeronautics.sc.gov/airport-development/sc-airport-capital-proj</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="141" t="s">
-        <v>787</v>
-      </c>
-      <c r="B41" s="145" t="n">
+      <c r="A41" s="144" t="s">
+        <v>807</v>
+      </c>
+      <c r="B41" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Cold Milling",Pay_Items!$D:$F,3,0),"")</f>
         <v>5</v>
       </c>
-      <c r="C41" s="141" t="s">
-        <v>780</v>
-      </c>
-      <c r="D41" s="141" t="s">
-        <v>788</v>
-      </c>
-      <c r="E41" s="142" t="n">
+      <c r="C41" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="D41" s="144" t="s">
+        <v>808</v>
+      </c>
+      <c r="E41" s="145" t="n">
         <v>2025</v>
       </c>
-      <c r="F41" s="141"/>
-      <c r="G41" s="144" t="str">
+      <c r="F41" s="144"/>
+      <c r="G41" s="147" t="str">
         <f aca="false">HYPERLINK("https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Rehab_Twy_A.pdf","https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Reha")</f>
         <v>https://aeronautics.sc.gov/sites/default/files/2025-05/250521_FLO_Reha</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="141" t="s">
-        <v>789</v>
-      </c>
-      <c r="B42" s="145" t="n">
+      <c r="A42" s="144" t="s">
+        <v>809</v>
+      </c>
+      <c r="B42" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Emulsified Asphalt Surface Treatment",Pay_Items!$D:$F,3,0),"")</f>
         <v>4</v>
       </c>
-      <c r="C42" s="141" t="s">
-        <v>780</v>
-      </c>
-      <c r="D42" s="141" t="s">
-        <v>790</v>
-      </c>
-      <c r="E42" s="142" t="n">
+      <c r="C42" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="D42" s="144" t="s">
+        <v>810</v>
+      </c>
+      <c r="E42" s="145" t="n">
         <v>2022</v>
       </c>
-      <c r="F42" s="141" t="s">
-        <v>791</v>
-      </c>
-      <c r="G42" s="144" t="str">
+      <c r="F42" s="144" t="s">
+        <v>811</v>
+      </c>
+      <c r="G42" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tn.gov/tdot/aeronautics/apmm-contract.html","https://www.tn.gov/tdot/aeronautics/apmm-contract.html")</f>
         <v>https://www.tn.gov/tdot/aeronautics/apmm-contract.html</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="141" t="s">
-        <v>792</v>
-      </c>
-      <c r="B43" s="145" t="n">
+      <c r="A43" s="144" t="s">
+        <v>812</v>
+      </c>
+      <c r="B43" s="148" t="n">
         <f aca="false">IFERROR(VLOOKUP("Markings (prep, markings, reflective media)",Pay_Items!$D:$F,3,0),"")</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="C43" s="141" t="s">
-        <v>793</v>
-      </c>
-      <c r="D43" s="141" t="s">
-        <v>790</v>
-      </c>
-      <c r="E43" s="142" t="n">
+      <c r="C43" s="144" t="s">
+        <v>813</v>
+      </c>
+      <c r="D43" s="144" t="s">
+        <v>810</v>
+      </c>
+      <c r="E43" s="145" t="n">
         <v>2022</v>
       </c>
-      <c r="F43" s="141"/>
-      <c r="G43" s="144" t="str">
+      <c r="F43" s="144"/>
+      <c r="G43" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tn.gov/tdot/aeronautics/apmm-contract.html","https://www.tn.gov/tdot/aeronautics/apmm-contract.html")</f>
         <v>https://www.tn.gov/tdot/aeronautics/apmm-contract.html</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="141" t="s">
-        <v>794</v>
-      </c>
-      <c r="B44" s="141"/>
-      <c r="C44" s="141" t="s">
-        <v>780</v>
-      </c>
-      <c r="D44" s="141" t="s">
-        <v>795</v>
-      </c>
-      <c r="E44" s="142" t="n">
+      <c r="A44" s="144" t="s">
+        <v>814</v>
+      </c>
+      <c r="B44" s="144"/>
+      <c r="C44" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="D44" s="144" t="s">
+        <v>815</v>
+      </c>
+      <c r="E44" s="145" t="n">
         <v>2025</v>
       </c>
-      <c r="F44" s="141" t="s">
-        <v>796</v>
-      </c>
-      <c r="G44" s="144" t="str">
+      <c r="F44" s="144" t="s">
+        <v>816</v>
+      </c>
+      <c r="G44" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-grand-opening","https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-gr")</f>
         <v>https://www.smyrnaairport.com/news-events/smyrna-airport-runway-119-gr</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="141" t="s">
-        <v>797</v>
-      </c>
-      <c r="B45" s="142" t="n">
+      <c r="A45" s="144" t="s">
+        <v>817</v>
+      </c>
+      <c r="B45" s="145" t="n">
         <v>820000</v>
       </c>
-      <c r="C45" s="141" t="s">
-        <v>715</v>
-      </c>
-      <c r="D45" s="141"/>
-      <c r="E45" s="142" t="n">
+      <c r="C45" s="144" t="s">
+        <v>735</v>
+      </c>
+      <c r="D45" s="144"/>
+      <c r="E45" s="145" t="n">
         <v>2023</v>
       </c>
-      <c r="F45" s="141" t="s">
-        <v>798</v>
-      </c>
-      <c r="G45" s="144" t="str">
+      <c r="F45" s="144" t="s">
+        <v>818</v>
+      </c>
+      <c r="G45" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.stategazette.com/news/regional-airport-receives-state-grant/article_5fd852fd-1d67-525c-b6fc-b32fbc676bdc.html","https://www.stategazette.com/news/regional-airport-receives-state-gran")</f>
         <v>https://www.stategazette.com/news/regional-airport-receives-state-gran</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="140" t="s">
-        <v>799</v>
-      </c>
-      <c r="B46" s="140"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="140"/>
+      <c r="A46" s="143" t="s">
+        <v>819</v>
+      </c>
+      <c r="B46" s="143"/>
+      <c r="C46" s="143"/>
+      <c r="D46" s="143"/>
+      <c r="E46" s="143"/>
+      <c r="F46" s="143"/>
+      <c r="G46" s="143"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="135" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="B48" s="136"/>
       <c r="C48" s="136"/>
@@ -32306,224 +34014,224 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="128" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="B49" s="128" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="C49" s="128" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="D49" s="128" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="E49" s="128" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="F49" s="128"/>
       <c r="G49" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="141" t="s">
-        <v>805</v>
-      </c>
-      <c r="B50" s="141" t="s">
-        <v>806</v>
-      </c>
-      <c r="C50" s="141" t="n">
+      <c r="A50" s="144" t="s">
+        <v>825</v>
+      </c>
+      <c r="B50" s="144" t="s">
+        <v>826</v>
+      </c>
+      <c r="C50" s="144" t="n">
         <f aca="false">ROUNDUP(66667/15000,0)</f>
         <v>5</v>
       </c>
-      <c r="D50" s="141" t="s">
-        <v>807</v>
-      </c>
-      <c r="E50" s="141" t="s">
-        <v>808</v>
-      </c>
-      <c r="F50" s="141"/>
-      <c r="G50" s="141" t="s">
-        <v>809</v>
+      <c r="D50" s="144" t="s">
+        <v>827</v>
+      </c>
+      <c r="E50" s="144" t="s">
+        <v>828</v>
+      </c>
+      <c r="F50" s="144"/>
+      <c r="G50" s="144" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="141" t="s">
-        <v>810</v>
-      </c>
-      <c r="B51" s="141" t="s">
-        <v>811</v>
-      </c>
-      <c r="C51" s="141" t="n">
+      <c r="A51" s="144" t="s">
+        <v>830</v>
+      </c>
+      <c r="B51" s="144" t="s">
+        <v>831</v>
+      </c>
+      <c r="C51" s="144" t="n">
         <f aca="false">ROUNDUP(15000/20000,0)+ROUNDUP(15000/50000,0)</f>
         <v>2</v>
       </c>
-      <c r="D51" s="141" t="s">
-        <v>812</v>
-      </c>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
-      <c r="G51" s="141" t="s">
-        <v>813</v>
+      <c r="D51" s="144" t="s">
+        <v>832</v>
+      </c>
+      <c r="E51" s="144"/>
+      <c r="F51" s="144"/>
+      <c r="G51" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="141" t="s">
-        <v>814</v>
-      </c>
-      <c r="B52" s="141" t="s">
-        <v>815</v>
-      </c>
-      <c r="C52" s="141" t="n">
+      <c r="A52" s="144" t="s">
+        <v>834</v>
+      </c>
+      <c r="B52" s="144" t="s">
+        <v>835</v>
+      </c>
+      <c r="C52" s="144" t="n">
         <f aca="false">ROUNDUP(66667*0.0075/10000,0)</f>
         <v>1</v>
       </c>
-      <c r="D52" s="141" t="s">
-        <v>816</v>
-      </c>
-      <c r="E52" s="141"/>
-      <c r="F52" s="141"/>
-      <c r="G52" s="141" t="s">
-        <v>813</v>
+      <c r="D52" s="144" t="s">
+        <v>836</v>
+      </c>
+      <c r="E52" s="144"/>
+      <c r="F52" s="144"/>
+      <c r="G52" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="141" t="s">
-        <v>817</v>
-      </c>
-      <c r="B53" s="141" t="s">
-        <v>818</v>
-      </c>
-      <c r="C53" s="141" t="n">
+      <c r="A53" s="144" t="s">
+        <v>837</v>
+      </c>
+      <c r="B53" s="144" t="s">
+        <v>838</v>
+      </c>
+      <c r="C53" s="144" t="n">
         <f aca="false">ROUNDUP(66667*0.0325/5000,0)</f>
         <v>1</v>
       </c>
-      <c r="D53" s="141" t="s">
-        <v>816</v>
-      </c>
-      <c r="E53" s="141"/>
-      <c r="F53" s="141"/>
-      <c r="G53" s="141" t="s">
-        <v>813</v>
+      <c r="D53" s="144" t="s">
+        <v>836</v>
+      </c>
+      <c r="E53" s="144"/>
+      <c r="F53" s="144"/>
+      <c r="G53" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="141" t="s">
-        <v>819</v>
-      </c>
-      <c r="B54" s="141" t="s">
-        <v>820</v>
-      </c>
-      <c r="C54" s="141" t="n">
+      <c r="A54" s="144" t="s">
+        <v>839</v>
+      </c>
+      <c r="B54" s="144" t="s">
+        <v>840</v>
+      </c>
+      <c r="C54" s="144" t="n">
         <f aca="false">ROUNDUP(66667/3800,0)+ROUNDUP(15000/50000,0)</f>
         <v>19</v>
       </c>
-      <c r="D54" s="141" t="s">
-        <v>821</v>
-      </c>
-      <c r="E54" s="141" t="s">
-        <v>822</v>
-      </c>
-      <c r="F54" s="141"/>
-      <c r="G54" s="141" t="s">
-        <v>813</v>
+      <c r="D54" s="144" t="s">
+        <v>841</v>
+      </c>
+      <c r="E54" s="144" t="s">
+        <v>842</v>
+      </c>
+      <c r="F54" s="144"/>
+      <c r="G54" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="141" t="s">
-        <v>823</v>
-      </c>
-      <c r="B55" s="141" t="s">
-        <v>824</v>
-      </c>
-      <c r="C55" s="141" t="n">
+      <c r="A55" s="144" t="s">
+        <v>843</v>
+      </c>
+      <c r="B55" s="144" t="s">
+        <v>844</v>
+      </c>
+      <c r="C55" s="144" t="n">
         <f aca="false">ROUNDUP(66667*550/(50*100/9)/10000,0)</f>
         <v>7</v>
       </c>
-      <c r="D55" s="141" t="s">
-        <v>825</v>
-      </c>
-      <c r="E55" s="141"/>
-      <c r="F55" s="141"/>
-      <c r="G55" s="141" t="s">
-        <v>813</v>
+      <c r="D55" s="144" t="s">
+        <v>845</v>
+      </c>
+      <c r="E55" s="144"/>
+      <c r="F55" s="144"/>
+      <c r="G55" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="141" t="s">
-        <v>826</v>
-      </c>
-      <c r="B56" s="141" t="s">
-        <v>827</v>
-      </c>
-      <c r="C56" s="141" t="n">
+      <c r="A56" s="144" t="s">
+        <v>846</v>
+      </c>
+      <c r="B56" s="144" t="s">
+        <v>847</v>
+      </c>
+      <c r="C56" s="144" t="n">
         <f aca="false">ROUNDUP(66667*0.003/10000,0)+ROUNDUP(66667*0.0013/5000,0)+ROUNDUP(66667*0.0025/5000,0)</f>
         <v>3</v>
       </c>
-      <c r="D56" s="141" t="s">
-        <v>828</v>
-      </c>
-      <c r="E56" s="141"/>
-      <c r="F56" s="141"/>
-      <c r="G56" s="141" t="s">
-        <v>813</v>
+      <c r="D56" s="144" t="s">
+        <v>848</v>
+      </c>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="141" t="s">
-        <v>829</v>
-      </c>
-      <c r="B57" s="141" t="s">
-        <v>830</v>
-      </c>
-      <c r="C57" s="141" t="n">
+      <c r="A57" s="144" t="s">
+        <v>849</v>
+      </c>
+      <c r="B57" s="144" t="s">
+        <v>850</v>
+      </c>
+      <c r="C57" s="144" t="n">
         <f aca="false">ROUNDUP(66667*0.02/1000,0)+7</f>
         <v>9</v>
       </c>
-      <c r="D57" s="141" t="s">
-        <v>831</v>
-      </c>
-      <c r="E57" s="141" t="s">
-        <v>832</v>
-      </c>
-      <c r="F57" s="141"/>
-      <c r="G57" s="141" t="s">
-        <v>813</v>
+      <c r="D57" s="144" t="s">
+        <v>851</v>
+      </c>
+      <c r="E57" s="144" t="s">
+        <v>852</v>
+      </c>
+      <c r="F57" s="144"/>
+      <c r="G57" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="141" t="s">
+      <c r="A58" s="144" t="s">
+        <v>853</v>
+      </c>
+      <c r="B58" s="144"/>
+      <c r="C58" s="144" t="s">
+        <v>854</v>
+      </c>
+      <c r="D58" s="144" t="s">
+        <v>855</v>
+      </c>
+      <c r="E58" s="144" t="s">
+        <v>856</v>
+      </c>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144" t="s">
         <v>833</v>
       </c>
-      <c r="B58" s="141"/>
-      <c r="C58" s="141" t="s">
-        <v>834</v>
-      </c>
-      <c r="D58" s="141" t="s">
-        <v>835</v>
-      </c>
-      <c r="E58" s="141" t="s">
-        <v>836</v>
-      </c>
-      <c r="F58" s="141"/>
-      <c r="G58" s="141" t="s">
-        <v>813</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="140" t="s">
-        <v>837</v>
-      </c>
-      <c r="B59" s="140"/>
-      <c r="C59" s="140"/>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="140"/>
+      <c r="A59" s="143" t="s">
+        <v>857</v>
+      </c>
+      <c r="B59" s="143"/>
+      <c r="C59" s="143"/>
+      <c r="D59" s="143"/>
+      <c r="E59" s="143"/>
+      <c r="F59" s="143"/>
+      <c r="G59" s="143"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="135" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B61" s="136"/>
       <c r="C61" s="136"/>
@@ -32534,285 +34242,285 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="128" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B62" s="128" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="C62" s="128" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="D62" s="128" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="128"/>
       <c r="F62" s="128" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="G62" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="141" t="s">
-        <v>841</v>
-      </c>
-      <c r="B63" s="145" t="n">
+      <c r="A63" s="144" t="s">
+        <v>861</v>
+      </c>
+      <c r="B63" s="148" t="n">
         <f aca="false">'General Information'!$D$34</f>
         <v>3</v>
       </c>
-      <c r="C63" s="141" t="s">
-        <v>842</v>
-      </c>
-      <c r="D63" s="141"/>
-      <c r="E63" s="141"/>
-      <c r="F63" s="141" t="s">
-        <v>843</v>
-      </c>
-      <c r="G63" s="141" t="s">
-        <v>813</v>
+      <c r="C63" s="144" t="s">
+        <v>862</v>
+      </c>
+      <c r="D63" s="144"/>
+      <c r="E63" s="144"/>
+      <c r="F63" s="144" t="s">
+        <v>863</v>
+      </c>
+      <c r="G63" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="141" t="s">
-        <v>844</v>
-      </c>
-      <c r="B64" s="145" t="n">
+      <c r="A64" s="144" t="s">
+        <v>864</v>
+      </c>
+      <c r="B64" s="148" t="n">
         <f aca="false">'General Information'!$D$33</f>
         <v>30</v>
       </c>
-      <c r="C64" s="141" t="s">
-        <v>845</v>
-      </c>
-      <c r="D64" s="141"/>
-      <c r="E64" s="141"/>
-      <c r="F64" s="141" t="s">
-        <v>846</v>
-      </c>
-      <c r="G64" s="141" t="s">
-        <v>813</v>
+      <c r="C64" s="144" t="s">
+        <v>865</v>
+      </c>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
+      <c r="F64" s="144" t="s">
+        <v>866</v>
+      </c>
+      <c r="G64" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="141" t="s">
-        <v>847</v>
-      </c>
-      <c r="B65" s="141" t="s">
-        <v>848</v>
-      </c>
-      <c r="C65" s="141" t="s">
-        <v>842</v>
-      </c>
-      <c r="D65" s="143" t="n">
+      <c r="A65" s="144" t="s">
+        <v>867</v>
+      </c>
+      <c r="B65" s="144" t="s">
+        <v>868</v>
+      </c>
+      <c r="C65" s="144" t="s">
+        <v>862</v>
+      </c>
+      <c r="D65" s="146" t="n">
         <v>2022</v>
       </c>
-      <c r="E65" s="141"/>
-      <c r="F65" s="141" t="s">
-        <v>849</v>
-      </c>
-      <c r="G65" s="144" t="str">
+      <c r="E65" s="144"/>
+      <c r="F65" s="144" t="s">
+        <v>869</v>
+      </c>
+      <c r="G65" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/airports/aip/guidance_letters/aip_pgl_22_01","https://www.faa.gov/airports/aip/guidance_letters/aip_pgl_22_01")</f>
         <v>https://www.faa.gov/airports/aip/guidance_letters/aip_pgl_22_01</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="141" t="s">
-        <v>850</v>
-      </c>
-      <c r="B66" s="142" t="n">
+      <c r="A66" s="144" t="s">
+        <v>870</v>
+      </c>
+      <c r="B66" s="145" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="141" t="s">
-        <v>842</v>
-      </c>
-      <c r="D66" s="143" t="n">
+      <c r="C66" s="144" t="s">
+        <v>862</v>
+      </c>
+      <c r="D66" s="146" t="n">
         <v>2026</v>
       </c>
-      <c r="E66" s="141"/>
-      <c r="F66" s="141" t="s">
-        <v>851</v>
-      </c>
-      <c r="G66" s="144" t="str">
+      <c r="E66" s="144"/>
+      <c r="F66" s="144" t="s">
+        <v>871</v>
+      </c>
+      <c r="G66" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.whitehouse.gov/wp-content/uploads/2026/03/CircularA-94Appendix-C.pdf","https://www.whitehouse.gov/wp-content/uploads/2026/03/CircularA-94Appe")</f>
         <v>https://www.whitehouse.gov/wp-content/uploads/2026/03/CircularA-94Appe</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="141" t="s">
-        <v>852</v>
-      </c>
-      <c r="B67" s="141" t="s">
-        <v>853</v>
-      </c>
-      <c r="C67" s="141"/>
-      <c r="D67" s="143" t="n">
+      <c r="A67" s="144" t="s">
+        <v>872</v>
+      </c>
+      <c r="B67" s="144" t="s">
+        <v>873</v>
+      </c>
+      <c r="C67" s="144"/>
+      <c r="D67" s="146" t="n">
         <v>2014</v>
       </c>
-      <c r="E67" s="141"/>
-      <c r="F67" s="141" t="s">
-        <v>854</v>
-      </c>
-      <c r="G67" s="144" t="str">
+      <c r="E67" s="144"/>
+      <c r="F67" s="144" t="s">
+        <v>874</v>
+      </c>
+      <c r="G67" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.whitehouse.gov/wp-content/uploads/2025/02/M-25-23-Rescission-and-Reinstatement-of-Circular-No.-A-94.pdf","https://www.whitehouse.gov/wp-content/uploads/2025/02/M-25-23-Rescissi")</f>
         <v>https://www.whitehouse.gov/wp-content/uploads/2025/02/M-25-23-Rescissi</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="141" t="s">
-        <v>855</v>
-      </c>
-      <c r="B68" s="141" t="s">
-        <v>856</v>
-      </c>
-      <c r="C68" s="141"/>
-      <c r="D68" s="143" t="n">
+      <c r="A68" s="144" t="s">
+        <v>875</v>
+      </c>
+      <c r="B68" s="144" t="s">
+        <v>876</v>
+      </c>
+      <c r="C68" s="144"/>
+      <c r="D68" s="146" t="n">
         <v>2009</v>
       </c>
-      <c r="E68" s="141"/>
-      <c r="F68" s="141" t="s">
-        <v>857</v>
-      </c>
-      <c r="G68" s="144" t="str">
+      <c r="E68" s="144"/>
+      <c r="F68" s="144" t="s">
+        <v>877</v>
+      </c>
+      <c r="G68" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/documentLibrary/media/Advisory_Circular/150_5320_6e_part4.pdf","https://www.faa.gov/documentLibrary/media/Advisory_Circular/150_5320_6")</f>
         <v>https://www.faa.gov/documentLibrary/media/Advisory_Circular/150_5320_6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="141" t="s">
-        <v>858</v>
-      </c>
-      <c r="B69" s="141" t="s">
-        <v>859</v>
-      </c>
-      <c r="C69" s="141"/>
-      <c r="D69" s="143" t="n">
+      <c r="A69" s="144" t="s">
+        <v>878</v>
+      </c>
+      <c r="B69" s="144" t="s">
+        <v>879</v>
+      </c>
+      <c r="C69" s="144"/>
+      <c r="D69" s="146" t="n">
         <v>2011</v>
       </c>
-      <c r="E69" s="141"/>
-      <c r="F69" s="141" t="s">
-        <v>860</v>
-      </c>
-      <c r="G69" s="144" t="str">
+      <c r="E69" s="144"/>
+      <c r="F69" s="144" t="s">
+        <v>880</v>
+      </c>
+      <c r="G69" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Final.06-06.pdf","https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Fi")</f>
         <v>https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Fi</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="141" t="s">
-        <v>861</v>
-      </c>
-      <c r="B70" s="141" t="s">
-        <v>862</v>
-      </c>
-      <c r="C70" s="141"/>
-      <c r="D70" s="143" t="n">
+      <c r="A70" s="144" t="s">
+        <v>881</v>
+      </c>
+      <c r="B70" s="144" t="s">
+        <v>882</v>
+      </c>
+      <c r="C70" s="144"/>
+      <c r="D70" s="146" t="n">
         <v>2013</v>
       </c>
-      <c r="E70" s="141"/>
-      <c r="F70" s="141" t="s">
-        <v>863</v>
-      </c>
-      <c r="G70" s="144" t="str">
+      <c r="E70" s="144"/>
+      <c r="F70" s="144" t="s">
+        <v>883</v>
+      </c>
+      <c r="G70" s="147" t="str">
         <f aca="false">HYPERLINK("https://dot.ca.gov/-/media/dot-media/programs/maintenance/documents/office-of-concrete-pavement/life-cycle-cost-analysis/lcca-25ca-manual-final-aug-1-2013-v2-a11y.pdf","https://dot.ca.gov/-/media/dot-media/programs/maintenance/documents/of")</f>
         <v>https://dot.ca.gov/-/media/dot-media/programs/maintenance/documents/of</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="141" t="s">
-        <v>864</v>
-      </c>
-      <c r="B71" s="142" t="n">
+      <c r="A71" s="144" t="s">
+        <v>884</v>
+      </c>
+      <c r="B71" s="145" t="n">
         <v>20</v>
       </c>
-      <c r="C71" s="141" t="s">
-        <v>845</v>
-      </c>
-      <c r="D71" s="143" t="n">
+      <c r="C71" s="144" t="s">
+        <v>865</v>
+      </c>
+      <c r="D71" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E71" s="141"/>
-      <c r="F71" s="141" t="s">
-        <v>865</v>
-      </c>
-      <c r="G71" s="144" t="str">
+      <c r="E71" s="144"/>
+      <c r="F71" s="144" t="s">
+        <v>885</v>
+      </c>
+      <c r="G71" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6G-Pavement-Design.pdf","https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6")</f>
         <v>https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="141" t="s">
-        <v>866</v>
-      </c>
-      <c r="B72" s="145" t="n">
+      <c r="A72" s="144" t="s">
+        <v>886</v>
+      </c>
+      <c r="B72" s="148" t="n">
         <f aca="false">'Maintenance Policies'!$D$32</f>
         <v>0.125</v>
       </c>
-      <c r="C72" s="141" t="s">
-        <v>867</v>
-      </c>
-      <c r="D72" s="141"/>
-      <c r="E72" s="141"/>
-      <c r="F72" s="141" t="s">
-        <v>868</v>
-      </c>
-      <c r="G72" s="141" t="s">
-        <v>813</v>
+      <c r="C72" s="144" t="s">
+        <v>887</v>
+      </c>
+      <c r="D72" s="144"/>
+      <c r="E72" s="144"/>
+      <c r="F72" s="144" t="s">
+        <v>888</v>
+      </c>
+      <c r="G72" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="141" t="s">
-        <v>869</v>
-      </c>
-      <c r="B73" s="145" t="n">
+      <c r="A73" s="144" t="s">
+        <v>889</v>
+      </c>
+      <c r="B73" s="148" t="n">
         <f aca="false">'Maintenance Policies'!$D$46</f>
         <v>0.25</v>
       </c>
-      <c r="C73" s="141" t="s">
-        <v>870</v>
-      </c>
-      <c r="D73" s="141"/>
-      <c r="E73" s="141"/>
-      <c r="F73" s="141" t="s">
-        <v>871</v>
-      </c>
-      <c r="G73" s="141" t="s">
-        <v>813</v>
+      <c r="C73" s="144" t="s">
+        <v>890</v>
+      </c>
+      <c r="D73" s="144"/>
+      <c r="E73" s="144"/>
+      <c r="F73" s="144" t="s">
+        <v>891</v>
+      </c>
+      <c r="G73" s="144" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="141" t="s">
-        <v>872</v>
-      </c>
-      <c r="B74" s="141" t="s">
-        <v>873</v>
-      </c>
-      <c r="C74" s="141"/>
-      <c r="D74" s="143" t="n">
+      <c r="A74" s="144" t="s">
+        <v>892</v>
+      </c>
+      <c r="B74" s="144" t="s">
+        <v>893</v>
+      </c>
+      <c r="C74" s="144"/>
+      <c r="D74" s="146" t="n">
         <v>2011</v>
       </c>
-      <c r="E74" s="141"/>
-      <c r="F74" s="141" t="s">
-        <v>874</v>
-      </c>
-      <c r="G74" s="144" t="str">
+      <c r="E74" s="144"/>
+      <c r="F74" s="144" t="s">
+        <v>894</v>
+      </c>
+      <c r="G74" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Final.06-06.pdf","https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Fi")</f>
         <v>https://www.eng.auburn.edu/research/centers/ncat/files/aaptp/Report.Fi</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="140" t="s">
-        <v>875</v>
-      </c>
-      <c r="B75" s="140"/>
-      <c r="C75" s="140"/>
-      <c r="D75" s="140"/>
-      <c r="E75" s="140"/>
-      <c r="F75" s="140"/>
-      <c r="G75" s="140"/>
+      <c r="A75" s="143" t="s">
+        <v>895</v>
+      </c>
+      <c r="B75" s="143"/>
+      <c r="C75" s="143"/>
+      <c r="D75" s="143"/>
+      <c r="E75" s="143"/>
+      <c r="F75" s="143"/>
+      <c r="G75" s="143"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="135" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="B77" s="136"/>
       <c r="C77" s="136"/>
@@ -32826,205 +34534,205 @@
         <v>30</v>
       </c>
       <c r="B78" s="128" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="C78" s="128" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="D78" s="128" t="s">
         <v>35</v>
       </c>
       <c r="E78" s="128"/>
       <c r="F78" s="128" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="G78" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="141" t="s">
-        <v>879</v>
-      </c>
-      <c r="B79" s="145" t="str">
+      <c r="A79" s="144" t="s">
+        <v>899</v>
+      </c>
+      <c r="B79" s="148" t="str">
         <f aca="false">"years "&amp;'Maintenance Policies'!$E$10&amp;", "&amp;'Maintenance Policies'!$E$12&amp;", "&amp;'Maintenance Policies'!$E$26</f>
         <v>years 4, 8, 24</v>
       </c>
-      <c r="C79" s="141" t="s">
-        <v>880</v>
-      </c>
-      <c r="D79" s="143" t="n">
+      <c r="C79" s="144" t="s">
+        <v>900</v>
+      </c>
+      <c r="D79" s="146" t="n">
         <v>2014</v>
       </c>
-      <c r="E79" s="141"/>
-      <c r="F79" s="141" t="s">
-        <v>881</v>
-      </c>
-      <c r="G79" s="144" t="str">
+      <c r="E79" s="144"/>
+      <c r="F79" s="144" t="s">
+        <v>901</v>
+      </c>
+      <c r="G79" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-7b.pdf","https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-7")</f>
         <v>https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-7</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="141" t="s">
-        <v>882</v>
-      </c>
-      <c r="B80" s="145" t="str">
+      <c r="A80" s="144" t="s">
+        <v>902</v>
+      </c>
+      <c r="B80" s="148" t="str">
         <f aca="false">"years "&amp;'Maintenance Policies'!$E$14&amp;", "&amp;'Maintenance Policies'!$E$18&amp;", "&amp;'Maintenance Policies'!$E$28</f>
         <v>years 12, 16, 28</v>
       </c>
-      <c r="C80" s="141" t="s">
-        <v>883</v>
-      </c>
-      <c r="D80" s="143" t="n">
+      <c r="C80" s="144" t="s">
+        <v>903</v>
+      </c>
+      <c r="D80" s="146" t="n">
         <v>2014</v>
       </c>
-      <c r="E80" s="141"/>
-      <c r="F80" s="141"/>
-      <c r="G80" s="144" t="str">
+      <c r="E80" s="144"/>
+      <c r="F80" s="144"/>
+      <c r="G80" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-6c.pdf","https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-6")</f>
         <v>https://www.faa.gov/documentlibrary/media/advisory_circular/150-5380-6</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="141" t="s">
+      <c r="A81" s="144" t="s">
         <v>654</v>
       </c>
-      <c r="B81" s="145" t="str">
+      <c r="B81" s="148" t="str">
         <f aca="false">"year "&amp;'Maintenance Policies'!$E$22</f>
         <v>year 20</v>
       </c>
-      <c r="C81" s="141" t="s">
-        <v>884</v>
-      </c>
-      <c r="D81" s="143" t="n">
+      <c r="C81" s="144" t="s">
+        <v>904</v>
+      </c>
+      <c r="D81" s="146" t="n">
         <v>2014</v>
       </c>
-      <c r="E81" s="141"/>
-      <c r="F81" s="141" t="s">
-        <v>885</v>
-      </c>
-      <c r="G81" s="144" t="str">
+      <c r="E81" s="144"/>
+      <c r="F81" s="144" t="s">
+        <v>905</v>
+      </c>
+      <c r="G81" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goals-of-the-FAAs-Extended-Airport-Pavement-Life-Program.pdf","https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goa")</f>
         <v>https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goa</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="141" t="s">
-        <v>886</v>
-      </c>
-      <c r="B82" s="145" t="str">
+      <c r="A82" s="144" t="s">
+        <v>906</v>
+      </c>
+      <c r="B82" s="148" t="str">
         <f aca="false">"year "&amp;'Maintenance Policies'!$E$37</f>
         <v>year 19</v>
       </c>
-      <c r="C82" s="141" t="s">
-        <v>887</v>
-      </c>
-      <c r="D82" s="141"/>
-      <c r="E82" s="141"/>
-      <c r="F82" s="141" t="s">
-        <v>888</v>
-      </c>
-      <c r="G82" s="144" t="str">
+      <c r="C82" s="144" t="s">
+        <v>907</v>
+      </c>
+      <c r="D82" s="144"/>
+      <c r="E82" s="144"/>
+      <c r="F82" s="144" t="s">
+        <v>908</v>
+      </c>
+      <c r="G82" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.tarmacview.com/glossary/joint-sealant/","https://www.tarmacview.com/glossary/joint-sealant/")</f>
         <v>https://www.tarmacview.com/glossary/joint-sealant/</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="141" t="s">
-        <v>889</v>
-      </c>
-      <c r="B83" s="145" t="str">
+      <c r="A83" s="144" t="s">
+        <v>909</v>
+      </c>
+      <c r="B83" s="148" t="str">
         <f aca="false">"year "&amp;'Maintenance Policies'!$E$41</f>
         <v>year 27</v>
       </c>
-      <c r="C83" s="141" t="s">
-        <v>890</v>
-      </c>
-      <c r="D83" s="143" t="n">
+      <c r="C83" s="144" t="s">
+        <v>910</v>
+      </c>
+      <c r="D83" s="146" t="n">
         <v>2014</v>
       </c>
-      <c r="E83" s="141"/>
-      <c r="F83" s="141"/>
-      <c r="G83" s="144" t="str">
+      <c r="E83" s="144"/>
+      <c r="F83" s="144"/>
+      <c r="G83" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goals-of-the-FAAs-Extended-Airport-Pavement-Life-Program.pdf","https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goa")</f>
         <v>https://www.acpa.org/wp-content/uploads/2025/03/ACPA-Achieving-the-Goa</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="141" t="s">
-        <v>891</v>
-      </c>
-      <c r="B84" s="141" t="s">
-        <v>892</v>
-      </c>
-      <c r="C84" s="141" t="s">
-        <v>893</v>
-      </c>
-      <c r="D84" s="143" t="n">
+      <c r="A84" s="144" t="s">
+        <v>911</v>
+      </c>
+      <c r="B84" s="144" t="s">
+        <v>912</v>
+      </c>
+      <c r="C84" s="144" t="s">
+        <v>913</v>
+      </c>
+      <c r="D84" s="146" t="n">
         <v>2024</v>
       </c>
-      <c r="E84" s="141"/>
-      <c r="F84" s="141"/>
-      <c r="G84" s="144" t="str">
+      <c r="E84" s="144"/>
+      <c r="F84" s="144"/>
+      <c r="G84" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.airporttech.tc.faa.gov/Portals/0/FactSheets/Extended%20Airport%20Pavement%20Life%20Factsheet_May%202024.pdf","https://www.airporttech.tc.faa.gov/Portals/0/FactSheets/Extended%20Air")</f>
         <v>https://www.airporttech.tc.faa.gov/Portals/0/FactSheets/Extended%20Air</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="141" t="s">
-        <v>894</v>
-      </c>
-      <c r="B85" s="141"/>
-      <c r="C85" s="141" t="s">
-        <v>895</v>
-      </c>
-      <c r="D85" s="143" t="n">
+      <c r="A85" s="144" t="s">
+        <v>914</v>
+      </c>
+      <c r="B85" s="144"/>
+      <c r="C85" s="144" t="s">
+        <v>915</v>
+      </c>
+      <c r="D85" s="146" t="n">
         <v>2016</v>
       </c>
-      <c r="E85" s="141"/>
-      <c r="F85" s="141" t="s">
-        <v>896</v>
-      </c>
-      <c r="G85" s="144" t="str">
+      <c r="E85" s="144"/>
+      <c r="F85" s="144" t="s">
+        <v>916</v>
+      </c>
+      <c r="G85" s="147" t="str">
         <f aca="false">HYPERLINK("https://nap.nationalacademies.org/catalog/23649/","https://nap.nationalacademies.org/catalog/23649/")</f>
         <v>https://nap.nationalacademies.org/catalog/23649/</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="141" t="s">
-        <v>897</v>
-      </c>
-      <c r="B86" s="141"/>
-      <c r="C86" s="141" t="s">
-        <v>898</v>
-      </c>
-      <c r="D86" s="143" t="n">
+      <c r="A86" s="144" t="s">
+        <v>917</v>
+      </c>
+      <c r="B86" s="144"/>
+      <c r="C86" s="144" t="s">
+        <v>918</v>
+      </c>
+      <c r="D86" s="146" t="n">
         <v>2021</v>
       </c>
-      <c r="E86" s="141"/>
-      <c r="F86" s="141" t="s">
-        <v>899</v>
-      </c>
-      <c r="G86" s="144" t="str">
+      <c r="E86" s="144"/>
+      <c r="F86" s="144" t="s">
+        <v>919</v>
+      </c>
+      <c r="G86" s="147" t="str">
         <f aca="false">HYPERLINK("https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6G-Pavement-Design.pdf","https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6")</f>
         <v>https://www.faa.gov/documentLibrary/media/Advisory_Circular/150-5320-6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="140" t="s">
-        <v>900</v>
-      </c>
-      <c r="B87" s="140"/>
-      <c r="C87" s="140"/>
-      <c r="D87" s="140"/>
-      <c r="E87" s="140"/>
-      <c r="F87" s="140"/>
-      <c r="G87" s="140"/>
+      <c r="A87" s="143" t="s">
+        <v>920</v>
+      </c>
+      <c r="B87" s="143"/>
+      <c r="C87" s="143"/>
+      <c r="D87" s="143"/>
+      <c r="E87" s="143"/>
+      <c r="F87" s="143"/>
+      <c r="G87" s="143"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="135" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="B89" s="136"/>
       <c r="C89" s="136"/>
@@ -33035,481 +34743,481 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="128" t="s">
-        <v>902</v>
+        <v>922</v>
       </c>
       <c r="B90" s="128" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="C90" s="128" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="D90" s="128" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="E90" s="128" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="F90" s="128"/>
       <c r="G90" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="141" t="str">
+      <c r="A91" s="144" t="str">
         <f aca="false">IF(RevenueData!A2="","",RevenueData!A2)</f>
         <v>MKL</v>
       </c>
-      <c r="B91" s="145" t="n">
+      <c r="B91" s="148" t="n">
         <f aca="false">IF(A91="","",SUMIF(RevenueData!$A:$A,A91,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A91,RevenueData!$H:$H))</f>
         <v>8505.94</v>
       </c>
-      <c r="C91" s="141" t="n">
+      <c r="C91" s="144" t="n">
         <f aca="false">IF(A91="","",B91*7)</f>
         <v>59541.58</v>
       </c>
-      <c r="D91" s="141" t="n">
+      <c r="D91" s="144" t="n">
         <f aca="false">IF(A91="","",B91*19)</f>
         <v>161612.86</v>
       </c>
-      <c r="E91" s="141" t="str">
+      <c r="E91" s="144" t="str">
         <f aca="false">IF(A91="","",TRIM(IF(ISNUMBER(RevenueData!B2),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C2),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G2),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H2),"","other")))</f>
         <v>other</v>
       </c>
-      <c r="F91" s="141"/>
-      <c r="G91" s="141" t="s">
-        <v>907</v>
+      <c r="F91" s="144"/>
+      <c r="G91" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="141" t="str">
+      <c r="A92" s="144" t="str">
         <f aca="false">IF(RevenueData!A3="","",RevenueData!A3)</f>
         <v>SRB</v>
       </c>
-      <c r="B92" s="145" t="n">
+      <c r="B92" s="148" t="n">
         <f aca="false">IF(A92="","",SUMIF(RevenueData!$A:$A,A92,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A92,RevenueData!$H:$H))</f>
         <v>4344.12</v>
       </c>
-      <c r="C92" s="141" t="n">
+      <c r="C92" s="144" t="n">
         <f aca="false">IF(A92="","",B92*7)</f>
         <v>30408.84</v>
       </c>
-      <c r="D92" s="141" t="n">
+      <c r="D92" s="144" t="n">
         <f aca="false">IF(A92="","",B92*19)</f>
         <v>82538.28</v>
       </c>
-      <c r="E92" s="141" t="str">
+      <c r="E92" s="144" t="str">
         <f aca="false">IF(A92="","",TRIM(IF(ISNUMBER(RevenueData!B3),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C3),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G3),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H3),"","other")))</f>
         <v>other</v>
       </c>
-      <c r="F92" s="141"/>
-      <c r="G92" s="141" t="s">
-        <v>907</v>
+      <c r="F92" s="144"/>
+      <c r="G92" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="141" t="str">
+      <c r="A93" s="144" t="str">
         <f aca="false">IF(RevenueData!A4="","",RevenueData!A4)</f>
         <v>MBT</v>
       </c>
-      <c r="B93" s="145" t="n">
+      <c r="B93" s="148" t="n">
         <f aca="false">IF(A93="","",SUMIF(RevenueData!$A:$A,A93,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A93,RevenueData!$H:$H))</f>
         <v>8841.38</v>
       </c>
-      <c r="C93" s="141" t="n">
+      <c r="C93" s="144" t="n">
         <f aca="false">IF(A93="","",B93*7)</f>
         <v>61889.66</v>
       </c>
-      <c r="D93" s="141" t="n">
+      <c r="D93" s="144" t="n">
         <f aca="false">IF(A93="","",B93*19)</f>
         <v>167986.22</v>
       </c>
-      <c r="E93" s="141" t="str">
+      <c r="E93" s="144" t="str">
         <f aca="false">IF(A93="","",TRIM(IF(ISNUMBER(RevenueData!B4),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C4),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G4),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H4),"","other")))</f>
         <v>other</v>
       </c>
-      <c r="F93" s="141"/>
-      <c r="G93" s="141" t="s">
-        <v>907</v>
+      <c r="F93" s="144"/>
+      <c r="G93" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="141" t="str">
+      <c r="A94" s="144" t="str">
         <f aca="false">IF(RevenueData!A5="","",RevenueData!A5)</f>
         <v>NQA</v>
       </c>
-      <c r="B94" s="145" t="n">
+      <c r="B94" s="148" t="n">
         <f aca="false">IF(A94="","",SUMIF(RevenueData!$A:$A,A94,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A94,RevenueData!$H:$H))</f>
         <v>6291</v>
       </c>
-      <c r="C94" s="141" t="n">
+      <c r="C94" s="144" t="n">
         <f aca="false">IF(A94="","",B94*7)</f>
         <v>44037</v>
       </c>
-      <c r="D94" s="141" t="n">
+      <c r="D94" s="144" t="n">
         <f aca="false">IF(A94="","",B94*19)</f>
         <v>119529</v>
       </c>
-      <c r="E94" s="141" t="str">
+      <c r="E94" s="144" t="str">
         <f aca="false">IF(A94="","",TRIM(IF(ISNUMBER(RevenueData!B5),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C5),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G5),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H5),"","other")))</f>
         <v/>
       </c>
-      <c r="F94" s="141"/>
-      <c r="G94" s="141" t="s">
-        <v>907</v>
+      <c r="F94" s="144"/>
+      <c r="G94" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="141" t="str">
+      <c r="A95" s="144" t="str">
         <f aca="false">IF(RevenueData!A6="","",RevenueData!A6)</f>
         <v>DKX</v>
       </c>
-      <c r="B95" s="145" t="n">
+      <c r="B95" s="148" t="n">
         <f aca="false">IF(A95="","",SUMIF(RevenueData!$A:$A,A95,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A95,RevenueData!$H:$H))</f>
         <v>6703</v>
       </c>
-      <c r="C95" s="141" t="n">
+      <c r="C95" s="144" t="n">
         <f aca="false">IF(A95="","",B95*7)</f>
         <v>46921</v>
       </c>
-      <c r="D95" s="141" t="n">
+      <c r="D95" s="144" t="n">
         <f aca="false">IF(A95="","",B95*19)</f>
         <v>127357</v>
       </c>
-      <c r="E95" s="141" t="str">
+      <c r="E95" s="144" t="str">
         <f aca="false">IF(A95="","",TRIM(IF(ISNUMBER(RevenueData!B6),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C6),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G6),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H6),"","other")))</f>
         <v/>
       </c>
-      <c r="F95" s="141"/>
-      <c r="G95" s="141" t="s">
-        <v>907</v>
+      <c r="F95" s="144"/>
+      <c r="G95" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="141" t="str">
+      <c r="A96" s="144" t="str">
         <f aca="false">IF(RevenueData!A7="","",RevenueData!A7)</f>
         <v>SYI</v>
       </c>
-      <c r="B96" s="145" t="n">
+      <c r="B96" s="148" t="n">
         <f aca="false">IF(A96="","",SUMIF(RevenueData!$A:$A,A96,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A96,RevenueData!$H:$H))</f>
         <v>30816.64</v>
       </c>
-      <c r="C96" s="141" t="n">
+      <c r="C96" s="144" t="n">
         <f aca="false">IF(A96="","",B96*7)</f>
         <v>215716.48</v>
       </c>
-      <c r="D96" s="141" t="n">
+      <c r="D96" s="144" t="n">
         <f aca="false">IF(A96="","",B96*19)</f>
         <v>585516.16</v>
       </c>
-      <c r="E96" s="141" t="str">
+      <c r="E96" s="144" t="str">
         <f aca="false">IF(A96="","",TRIM(IF(ISNUMBER(RevenueData!B7),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C7),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G7),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H7),"","other")))</f>
         <v/>
       </c>
-      <c r="F96" s="141"/>
-      <c r="G96" s="141" t="s">
-        <v>907</v>
+      <c r="F96" s="144"/>
+      <c r="G96" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="141" t="str">
+      <c r="A97" s="144" t="str">
         <f aca="false">IF(RevenueData!A8="","",RevenueData!A8)</f>
         <v>GCY</v>
       </c>
-      <c r="B97" s="145" t="n">
+      <c r="B97" s="148" t="n">
         <f aca="false">IF(A97="","",SUMIF(RevenueData!$A:$A,A97,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A97,RevenueData!$H:$H))</f>
         <v>1800</v>
       </c>
-      <c r="C97" s="141" t="n">
+      <c r="C97" s="144" t="n">
         <f aca="false">IF(A97="","",B97*7)</f>
         <v>12600</v>
       </c>
-      <c r="D97" s="141" t="n">
+      <c r="D97" s="144" t="n">
         <f aca="false">IF(A97="","",B97*19)</f>
         <v>34200</v>
       </c>
-      <c r="E97" s="141" t="str">
+      <c r="E97" s="144" t="str">
         <f aca="false">IF(A97="","",TRIM(IF(ISNUMBER(RevenueData!B8),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C8),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G8),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H8),"","other")))</f>
         <v>tenant</v>
       </c>
-      <c r="F97" s="141"/>
-      <c r="G97" s="141" t="s">
-        <v>907</v>
+      <c r="F97" s="144"/>
+      <c r="G97" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="141" t="str">
+      <c r="A98" s="144" t="str">
         <f aca="false">IF(RevenueData!A9="","",RevenueData!A9)</f>
         <v>THA</v>
       </c>
-      <c r="B98" s="145" t="n">
+      <c r="B98" s="148" t="n">
         <f aca="false">IF(A98="","",SUMIF(RevenueData!$A:$A,A98,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A98,RevenueData!$H:$H))</f>
         <v>939.26</v>
       </c>
-      <c r="C98" s="141" t="n">
+      <c r="C98" s="144" t="n">
         <f aca="false">IF(A98="","",B98*7)</f>
         <v>6574.82</v>
       </c>
-      <c r="D98" s="141" t="n">
+      <c r="D98" s="144" t="n">
         <f aca="false">IF(A98="","",B98*19)</f>
         <v>17845.94</v>
       </c>
-      <c r="E98" s="141" t="str">
+      <c r="E98" s="144" t="str">
         <f aca="false">IF(A98="","",TRIM(IF(ISNUMBER(RevenueData!B9),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C9),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G9),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H9),"","other")))</f>
         <v>tenant</v>
       </c>
-      <c r="F98" s="141"/>
-      <c r="G98" s="141" t="s">
-        <v>907</v>
+      <c r="F98" s="144"/>
+      <c r="G98" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="141" t="str">
+      <c r="A99" s="144" t="str">
         <f aca="false">IF(RevenueData!A10="","",RevenueData!A10)</f>
         <v>GKT</v>
       </c>
-      <c r="B99" s="145" t="n">
+      <c r="B99" s="148" t="n">
         <f aca="false">IF(A99="","",SUMIF(RevenueData!$A:$A,A99,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A99,RevenueData!$H:$H))</f>
         <v>5441.17</v>
       </c>
-      <c r="C99" s="141" t="n">
+      <c r="C99" s="144" t="n">
         <f aca="false">IF(A99="","",B99*7)</f>
         <v>38088.19</v>
       </c>
-      <c r="D99" s="141" t="n">
+      <c r="D99" s="144" t="n">
         <f aca="false">IF(A99="","",B99*19)</f>
         <v>103382.23</v>
       </c>
-      <c r="E99" s="141" t="str">
+      <c r="E99" s="144" t="str">
         <f aca="false">IF(A99="","",TRIM(IF(ISNUMBER(RevenueData!B10),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C10),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G10),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H10),"","other")))</f>
         <v>tenant other</v>
       </c>
-      <c r="F99" s="141"/>
-      <c r="G99" s="141" t="s">
-        <v>907</v>
+      <c r="F99" s="144"/>
+      <c r="G99" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="141" t="str">
+      <c r="A100" s="144" t="str">
         <f aca="false">IF(RevenueData!A11="","",RevenueData!A11)</f>
         <v>JWN</v>
       </c>
-      <c r="B100" s="145" t="n">
+      <c r="B100" s="148" t="n">
         <f aca="false">IF(A100="","",SUMIF(RevenueData!$A:$A,A100,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A100,RevenueData!$H:$H))</f>
         <v>89240</v>
       </c>
-      <c r="C100" s="141" t="n">
+      <c r="C100" s="144" t="n">
         <f aca="false">IF(A100="","",B100*7)</f>
         <v>624680</v>
       </c>
-      <c r="D100" s="141" t="n">
+      <c r="D100" s="144" t="n">
         <f aca="false">IF(A100="","",B100*19)</f>
         <v>1695560</v>
       </c>
-      <c r="E100" s="141" t="str">
+      <c r="E100" s="144" t="str">
         <f aca="false">IF(A100="","",TRIM(IF(ISNUMBER(RevenueData!B11),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C11),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G11),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H11),"","other")))</f>
         <v>tenant</v>
       </c>
-      <c r="F100" s="141"/>
-      <c r="G100" s="141" t="s">
-        <v>907</v>
+      <c r="F100" s="144"/>
+      <c r="G100" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="141" t="str">
+      <c r="A101" s="144" t="str">
         <f aca="false">IF(RevenueData!A12="","",RevenueData!A12)</f>
         <v>MOR</v>
       </c>
-      <c r="B101" s="145" t="n">
+      <c r="B101" s="148" t="n">
         <f aca="false">IF(A101="","",SUMIF(RevenueData!$A:$A,A101,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A101,RevenueData!$H:$H))</f>
         <v>8801.4</v>
       </c>
-      <c r="C101" s="141" t="n">
+      <c r="C101" s="144" t="n">
         <f aca="false">IF(A101="","",B101*7)</f>
         <v>61609.8</v>
       </c>
-      <c r="D101" s="141" t="n">
+      <c r="D101" s="144" t="n">
         <f aca="false">IF(A101="","",B101*19)</f>
         <v>167226.6</v>
       </c>
-      <c r="E101" s="141" t="str">
+      <c r="E101" s="144" t="str">
         <f aca="false">IF(A101="","",TRIM(IF(ISNUMBER(RevenueData!B12),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C12),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G12),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H12),"","other")))</f>
         <v>tenant other</v>
       </c>
-      <c r="F101" s="141"/>
-      <c r="G101" s="141" t="s">
-        <v>907</v>
+      <c r="F101" s="144"/>
+      <c r="G101" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="141" t="str">
+      <c r="A102" s="144" t="str">
         <f aca="false">IF(RevenueData!A13="","",RevenueData!A13)</f>
         <v>MQY</v>
       </c>
-      <c r="B102" s="145" t="n">
+      <c r="B102" s="148" t="n">
         <f aca="false">IF(A102="","",SUMIF(RevenueData!$A:$A,A102,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A102,RevenueData!$H:$H))</f>
         <v>8841.38</v>
       </c>
-      <c r="C102" s="141" t="n">
+      <c r="C102" s="144" t="n">
         <f aca="false">IF(A102="","",B102*7)</f>
         <v>61889.66</v>
       </c>
-      <c r="D102" s="141" t="n">
+      <c r="D102" s="144" t="n">
         <f aca="false">IF(A102="","",B102*19)</f>
         <v>167986.22</v>
       </c>
-      <c r="E102" s="141" t="str">
+      <c r="E102" s="144" t="str">
         <f aca="false">IF(A102="","",TRIM(IF(ISNUMBER(RevenueData!B13),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C13),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G13),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H13),"","other")))</f>
         <v>other</v>
       </c>
-      <c r="F102" s="141"/>
-      <c r="G102" s="141" t="s">
-        <v>907</v>
+      <c r="F102" s="144"/>
+      <c r="G102" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="141" t="str">
+      <c r="A103" s="144" t="str">
         <f aca="false">IF(RevenueData!A14="","",RevenueData!A14)</f>
         <v>RZR</v>
       </c>
-      <c r="B103" s="145" t="n">
+      <c r="B103" s="148" t="n">
         <f aca="false">IF(A103="","",SUMIF(RevenueData!$A:$A,A103,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A103,RevenueData!$H:$H))</f>
         <v>4100</v>
       </c>
-      <c r="C103" s="141" t="n">
+      <c r="C103" s="144" t="n">
         <f aca="false">IF(A103="","",B103*7)</f>
         <v>28700</v>
       </c>
-      <c r="D103" s="141" t="n">
+      <c r="D103" s="144" t="n">
         <f aca="false">IF(A103="","",B103*19)</f>
         <v>77900</v>
       </c>
-      <c r="E103" s="141" t="str">
+      <c r="E103" s="144" t="str">
         <f aca="false">IF(A103="","",TRIM(IF(ISNUMBER(RevenueData!B14),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C14),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G14),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H14),"","other")))</f>
         <v/>
       </c>
-      <c r="F103" s="141"/>
-      <c r="G103" s="141" t="s">
-        <v>907</v>
+      <c r="F103" s="144"/>
+      <c r="G103" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="141" t="str">
+      <c r="A104" s="144" t="str">
         <f aca="false">IF(RevenueData!A15="","",RevenueData!A15)</f>
         <v>XNX</v>
       </c>
-      <c r="B104" s="145" t="n">
+      <c r="B104" s="148" t="n">
         <f aca="false">IF(A104="","",SUMIF(RevenueData!$A:$A,A104,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A104,RevenueData!$H:$H))</f>
         <v>81.97</v>
       </c>
-      <c r="C104" s="141" t="n">
+      <c r="C104" s="144" t="n">
         <f aca="false">IF(A104="","",B104*7)</f>
         <v>573.79</v>
       </c>
-      <c r="D104" s="141" t="n">
+      <c r="D104" s="144" t="n">
         <f aca="false">IF(A104="","",B104*19)</f>
         <v>1557.43</v>
       </c>
-      <c r="E104" s="141" t="str">
+      <c r="E104" s="144" t="str">
         <f aca="false">IF(A104="","",TRIM(IF(ISNUMBER(RevenueData!B15),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C15),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G15),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H15),"","other")))</f>
         <v>tenant other</v>
       </c>
-      <c r="F104" s="141"/>
-      <c r="G104" s="141" t="s">
-        <v>907</v>
+      <c r="F104" s="144"/>
+      <c r="G104" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="141" t="str">
+      <c r="A105" s="144" t="str">
         <f aca="false">IF(RevenueData!A16="","",RevenueData!A16)</f>
         <v>M91</v>
       </c>
-      <c r="B105" s="145" t="n">
+      <c r="B105" s="148" t="n">
         <f aca="false">IF(A105="","",SUMIF(RevenueData!$A:$A,A105,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A105,RevenueData!$H:$H))</f>
         <v>2058</v>
       </c>
-      <c r="C105" s="141" t="n">
+      <c r="C105" s="144" t="n">
         <f aca="false">IF(A105="","",B105*7)</f>
         <v>14406</v>
       </c>
-      <c r="D105" s="141" t="n">
+      <c r="D105" s="144" t="n">
         <f aca="false">IF(A105="","",B105*19)</f>
         <v>39102</v>
       </c>
-      <c r="E105" s="141" t="str">
+      <c r="E105" s="144" t="str">
         <f aca="false">IF(A105="","",TRIM(IF(ISNUMBER(RevenueData!B16),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C16),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G16),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H16),"","other")))</f>
         <v/>
       </c>
-      <c r="F105" s="141"/>
-      <c r="G105" s="141" t="s">
-        <v>907</v>
+      <c r="F105" s="144"/>
+      <c r="G105" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="141" t="str">
+      <c r="A106" s="144" t="str">
         <f aca="false">IF(RevenueData!A17="","",RevenueData!A17)</f>
         <v>CKV</v>
       </c>
-      <c r="B106" s="145" t="n">
+      <c r="B106" s="148" t="n">
         <f aca="false">IF(A106="","",SUMIF(RevenueData!$A:$A,A106,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A106,RevenueData!$H:$H))</f>
         <v>3239.39</v>
       </c>
-      <c r="C106" s="141" t="n">
+      <c r="C106" s="144" t="n">
         <f aca="false">IF(A106="","",B106*7)</f>
         <v>22675.73</v>
       </c>
-      <c r="D106" s="141" t="n">
+      <c r="D106" s="144" t="n">
         <f aca="false">IF(A106="","",B106*19)</f>
         <v>61548.41</v>
       </c>
-      <c r="E106" s="141" t="str">
+      <c r="E106" s="144" t="str">
         <f aca="false">IF(A106="","",TRIM(IF(ISNUMBER(RevenueData!B17),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C17),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G17),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H17),"","other")))</f>
         <v>tenant other</v>
       </c>
-      <c r="F106" s="141"/>
-      <c r="G106" s="141" t="s">
-        <v>907</v>
+      <c r="F106" s="144"/>
+      <c r="G106" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="141" t="str">
+      <c r="A107" s="144" t="str">
         <f aca="false">IF(RevenueData!A18="","",RevenueData!A18)</f>
         <v>M54</v>
       </c>
-      <c r="B107" s="145" t="n">
+      <c r="B107" s="148" t="n">
         <f aca="false">IF(A107="","",SUMIF(RevenueData!$A:$A,A107,RevenueData!$B:$B)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$C:$C)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$D:$D)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$E:$E)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$F:$F)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$G:$G)+SUMIF(RevenueData!$A:$A,A107,RevenueData!$H:$H))</f>
         <v>1027.81</v>
       </c>
-      <c r="C107" s="141" t="n">
+      <c r="C107" s="144" t="n">
         <f aca="false">IF(A107="","",B107*7)</f>
         <v>7194.67</v>
       </c>
-      <c r="D107" s="141" t="n">
+      <c r="D107" s="144" t="n">
         <f aca="false">IF(A107="","",B107*19)</f>
         <v>19528.39</v>
       </c>
-      <c r="E107" s="141" t="str">
+      <c r="E107" s="144" t="str">
         <f aca="false">IF(A107="","",TRIM(IF(ISNUMBER(RevenueData!B18),"","100LL ")&amp;IF(ISNUMBER(RevenueData!C18),"","Jet-A ")&amp;IF(ISNUMBER(RevenueData!G18),"","tenant ")&amp;IF(ISNUMBER(RevenueData!H18),"","other")))</f>
         <v>100LL Jet-A</v>
       </c>
-      <c r="F107" s="141"/>
-      <c r="G107" s="141" t="s">
-        <v>907</v>
+      <c r="F107" s="144"/>
+      <c r="G107" s="144" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="140" t="s">
-        <v>908</v>
-      </c>
-      <c r="B108" s="140"/>
-      <c r="C108" s="140"/>
-      <c r="D108" s="140"/>
-      <c r="E108" s="140"/>
-      <c r="F108" s="140"/>
-      <c r="G108" s="140"/>
+      <c r="A108" s="143" t="s">
+        <v>928</v>
+      </c>
+      <c r="B108" s="143"/>
+      <c r="C108" s="143"/>
+      <c r="D108" s="143"/>
+      <c r="E108" s="143"/>
+      <c r="F108" s="143"/>
+      <c r="G108" s="143"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="135" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="B110" s="136"/>
       <c r="C110" s="136"/>
@@ -33523,62 +35231,62 @@
         <v>30</v>
       </c>
       <c r="B111" s="128" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="C111" s="128"/>
       <c r="D111" s="128"/>
       <c r="E111" s="128"/>
       <c r="F111" s="128"/>
       <c r="G111" s="128" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="141" t="s">
-        <v>910</v>
-      </c>
-      <c r="B112" s="145" t="n">
+      <c r="A112" s="144" t="s">
+        <v>930</v>
+      </c>
+      <c r="B112" s="148" t="n">
         <f aca="false">COUNTA('General Information'!$L$10:$L$88)</f>
         <v>79</v>
       </c>
-      <c r="C112" s="141"/>
-      <c r="D112" s="141"/>
-      <c r="E112" s="141"/>
-      <c r="F112" s="141"/>
-      <c r="G112" s="141" t="s">
-        <v>911</v>
+      <c r="C112" s="144"/>
+      <c r="D112" s="144"/>
+      <c r="E112" s="144"/>
+      <c r="F112" s="144"/>
+      <c r="G112" s="144" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="141" t="s">
-        <v>912</v>
-      </c>
-      <c r="B113" s="145" t="n">
+      <c r="A113" s="144" t="s">
+        <v>932</v>
+      </c>
+      <c r="B113" s="148" t="n">
         <f aca="false">COUNTA(RevenueData!$A$2:$A$60)</f>
         <v>17</v>
       </c>
-      <c r="C113" s="141"/>
-      <c r="D113" s="141"/>
-      <c r="E113" s="141"/>
-      <c r="F113" s="141"/>
-      <c r="G113" s="141" t="s">
-        <v>913</v>
+      <c r="C113" s="144"/>
+      <c r="D113" s="144"/>
+      <c r="E113" s="144"/>
+      <c r="F113" s="144"/>
+      <c r="G113" s="144" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="141" t="s">
-        <v>914</v>
-      </c>
-      <c r="B114" s="145" t="str">
+      <c r="A114" s="144" t="s">
+        <v>934</v>
+      </c>
+      <c r="B114" s="148" t="str">
         <f aca="false">COUNTIF('General Information'!$P$10:$P$88,"Middle")&amp;" / "&amp;COUNTIF('General Information'!$P$10:$P$88,"West")&amp;" / "&amp;COUNTIF('General Information'!$P$10:$P$88,"East")</f>
         <v>33 / 21 / 25</v>
       </c>
-      <c r="C114" s="141"/>
-      <c r="D114" s="141"/>
-      <c r="E114" s="141"/>
-      <c r="F114" s="141"/>
-      <c r="G114" s="141" t="s">
-        <v>911</v>
+      <c r="C114" s="144"/>
+      <c r="D114" s="144"/>
+      <c r="E114" s="144"/>
+      <c r="F114" s="144"/>
+      <c r="G114" s="144" t="s">
+        <v>931</v>
       </c>
     </row>
   </sheetData>
